--- a/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_1_river_assess.xlsx
+++ b/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_1_river_assess.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\ONCHO\ento\river prospection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789442AD-A920-48AC-8FE8-5BA3615D372F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA08AC1C-19F2-463A-AE55-0DBE0CB9476E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="296">
   <si>
     <t>type</t>
   </si>
@@ -187,15 +187,9 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Oui</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Non</t>
-  </si>
-  <si>
     <t>Don't know</t>
   </si>
   <si>
@@ -220,12 +214,6 @@
     <t>vegetation_type</t>
   </si>
   <si>
-    <t>Végétation dense</t>
-  </si>
-  <si>
-    <t>Végétation clairsemée</t>
-  </si>
-  <si>
     <t>capture_point</t>
   </si>
   <si>
@@ -238,72 +226,21 @@
     <t>breeding_site_type</t>
   </si>
   <si>
-    <t>Artificiel</t>
-  </si>
-  <si>
-    <t>Naturel</t>
-  </si>
-  <si>
     <t>Permanent</t>
   </si>
   <si>
-    <t>Temporaire</t>
-  </si>
-  <si>
-    <t>Ancien.gite.OCP</t>
-  </si>
-  <si>
-    <t>Nouveau.gite</t>
-  </si>
-  <si>
     <t>village_activity</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
-    <t>Elevage</t>
-  </si>
-  <si>
-    <t>Unité.industrielle</t>
-  </si>
-  <si>
     <t>Other</t>
   </si>
   <si>
     <t>notes</t>
   </si>
   <si>
-    <t>Lessive.au.bord.des.cours.d.eau</t>
-  </si>
-  <si>
-    <t>Décharge.d.usine</t>
-  </si>
-  <si>
-    <t>Présence.de.tas.d.immondice</t>
-  </si>
-  <si>
-    <t>Variation.de.la.température</t>
-  </si>
-  <si>
-    <t>Humidité.relative</t>
-  </si>
-  <si>
-    <t>Changement.des.points.de.capture</t>
-  </si>
-  <si>
-    <t>Gite.frontalier.avec.a.la.RDC</t>
-  </si>
-  <si>
-    <t>Gite.frontalier.avec.a.la.Tanzanie</t>
-  </si>
-  <si>
-    <t>Gite.frontalier.au.Zanzibar</t>
-  </si>
-  <si>
     <t>form_title</t>
   </si>
   <si>
@@ -316,9 +253,6 @@
     <t>allow_choice_duplicates</t>
   </si>
   <si>
-    <t>demo_oncho_priv_prosp_9999_1_river_assess</t>
-  </si>
-  <si>
     <t>(Month yyyy) 1. ONCHO Ento Survey - River Inspection</t>
   </si>
   <si>
@@ -914,6 +848,81 @@
   </si>
   <si>
     <t>Works best outdoors</t>
+  </si>
+  <si>
+    <t>Old.OCP.site</t>
+  </si>
+  <si>
+    <t>New.site</t>
+  </si>
+  <si>
+    <t>Industrial.unit</t>
+  </si>
+  <si>
+    <t>Laundry.on.the.side.of.watercourses</t>
+  </si>
+  <si>
+    <t>Factory.discharge</t>
+  </si>
+  <si>
+    <t>Presence.of.waste.piles</t>
+  </si>
+  <si>
+    <t>Temperature.variation</t>
+  </si>
+  <si>
+    <t>Relative.humidity</t>
+  </si>
+  <si>
+    <t>Change.of.capture.points</t>
+  </si>
+  <si>
+    <t>Border.site.with.the.DRC</t>
+  </si>
+  <si>
+    <t>Border.site.with.Tanzania</t>
+  </si>
+  <si>
+    <t>Border.site.with.Zanzibar</t>
+  </si>
+  <si>
+    <t>demo_oncho_priv_prosp_9999_1_river_asses</t>
+  </si>
+  <si>
+    <t>s_densite</t>
+  </si>
+  <si>
+    <t>s_water_temp</t>
+  </si>
+  <si>
+    <t>s_water_ph</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>Larval density</t>
+  </si>
+  <si>
+    <t>Water temperature (°C)</t>
+  </si>
+  <si>
+    <t>select_one densite_List</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>. &gt; 0 and . &lt;=50</t>
+  </si>
+  <si>
+    <t>Please, enter  correct temperature</t>
+  </si>
+  <si>
+    <t>. &gt;= 0 and . &lt;= 14</t>
+  </si>
+  <si>
+    <t>Please enter a correct pH</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26" style="3" customWidth="1"/>
@@ -1424,10 +1433,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>2</v>
@@ -1436,7 +1445,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="H1" s="18" t="s">
         <v>4</v>
@@ -1454,21 +1463,21 @@
         <v>8</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1">
       <c r="A2" s="21" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="21"/>
@@ -1490,7 +1499,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="22"/>
@@ -1513,7 +1522,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="22"/>
@@ -1532,13 +1541,13 @@
     </row>
     <row r="5" spans="1:13" s="4" customFormat="1">
       <c r="A5" s="21" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="21"/>
@@ -1557,13 +1566,13 @@
     </row>
     <row r="6" spans="1:13" s="4" customFormat="1">
       <c r="A6" s="21" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="21"/>
@@ -1576,7 +1585,7 @@
       </c>
       <c r="K6" s="21"/>
       <c r="L6" s="21" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="M6" s="21"/>
     </row>
@@ -1585,17 +1594,17 @@
         <v>18</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
       <c r="G7" s="24"/>
       <c r="H7" s="21" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="I7" s="21"/>
       <c r="J7" s="21" t="s">
@@ -1607,20 +1616,20 @@
     </row>
     <row r="8" spans="1:13" s="4" customFormat="1">
       <c r="A8" s="21" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="I8" s="21"/>
       <c r="J8" s="21" t="s">
@@ -1628,26 +1637,26 @@
       </c>
       <c r="K8" s="21"/>
       <c r="L8" s="21" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:13" s="4" customFormat="1" ht="31.5">
       <c r="A9" s="21" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="24"/>
       <c r="H9" s="22" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22" t="s">
@@ -1655,7 +1664,7 @@
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="M9" s="21"/>
     </row>
@@ -1667,7 +1676,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="22"/>
@@ -1675,7 +1684,7 @@
       <c r="G10" s="24"/>
       <c r="H10" s="22"/>
       <c r="I10" s="22" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
@@ -1689,10 +1698,10 @@
         <v>18</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="22"/>
@@ -1700,7 +1709,7 @@
       <c r="G11" s="24"/>
       <c r="H11" s="22"/>
       <c r="I11" s="22" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
@@ -1717,7 +1726,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="21"/>
@@ -1740,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="D13" s="23"/>
       <c r="E13" s="21"/>
@@ -1763,7 +1772,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="21"/>
@@ -1771,114 +1780,122 @@
       <c r="G14" s="24"/>
       <c r="H14" s="21"/>
       <c r="I14" s="21"/>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="22" t="s">
         <v>11</v>
       </c>
       <c r="K14" s="21"/>
       <c r="L14" s="21"/>
       <c r="M14" s="21"/>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D15" s="27" t="s">
+    <row r="15" spans="1:13" s="4" customFormat="1">
+      <c r="A15" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="22"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+    </row>
+    <row r="16" spans="1:13" s="4" customFormat="1">
+      <c r="A16" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="21" t="s">
+      <c r="B16" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D16" s="23"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+    </row>
+    <row r="17" spans="1:13" s="4" customFormat="1">
+      <c r="A17" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="D17" s="23"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="26" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="D18" s="27"/>
+        <v>103</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>269</v>
+      </c>
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
       <c r="G18" s="27"/>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
-      <c r="J18" s="21"/>
+      <c r="J18" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
       <c r="M18" s="26"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="26" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="26"/>
@@ -1886,20 +1903,22 @@
       <c r="G19" s="27"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="21"/>
+      <c r="J19" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="K19" s="26"/>
       <c r="L19" s="26"/>
       <c r="M19" s="26"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="26"/>
@@ -1907,7 +1926,9 @@
       <c r="G20" s="27"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="21"/>
+      <c r="J20" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="M20" s="26"/>
@@ -1917,18 +1938,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="27"/>
-      <c r="H21" s="26" t="s">
-        <v>34</v>
-      </c>
+      <c r="H21" s="26"/>
       <c r="I21" s="26"/>
       <c r="J21" s="21"/>
       <c r="K21" s="26"/>
@@ -1937,100 +1956,104 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="26" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>292</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="D22" s="27"/>
       <c r="E22" s="26"/>
       <c r="F22" s="26"/>
       <c r="G22" s="27"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="21" t="s">
-        <v>11</v>
-      </c>
+      <c r="J22" s="21"/>
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
       <c r="M22" s="26"/>
     </row>
-    <row r="23" spans="1:13" s="4" customFormat="1">
-      <c r="A23" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-    </row>
-    <row r="24" spans="1:13" s="4" customFormat="1">
-      <c r="A24" s="21" t="s">
+    <row r="23" spans="1:13">
+      <c r="A23" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="27"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="24"/>
+      <c r="B24" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="27"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="27"/>
       <c r="H24" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" s="21"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-    </row>
-    <row r="25" spans="1:13" s="4" customFormat="1">
-      <c r="A25" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
+        <v>34</v>
+      </c>
+      <c r="I24" s="26"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1">
       <c r="A26" s="21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>111</v>
+      </c>
       <c r="D26" s="23"/>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
@@ -2043,19 +2066,80 @@
       <c r="M26" s="21"/>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1">
-      <c r="B27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="G27" s="3"/>
+      <c r="A27" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="23"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27" s="21"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1">
-      <c r="B28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="G28" s="3"/>
+      <c r="A28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1">
-      <c r="B29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="A29" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+    </row>
+    <row r="30" spans="1:13" s="4" customFormat="1">
+      <c r="B30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:13" s="4" customFormat="1">
+      <c r="B31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" s="4" customFormat="1">
+      <c r="B32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="G32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2084,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>46</v>
@@ -2093,21 +2177,21 @@
         <v>47</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="30"/>
@@ -2115,13 +2199,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="30"/>
@@ -2129,13 +2213,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="30"/>
@@ -2143,13 +2227,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="30"/>
@@ -2157,13 +2241,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="30"/>
@@ -2171,13 +2255,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="30"/>
@@ -2185,13 +2269,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="30"/>
@@ -2199,13 +2283,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="30"/>
@@ -2213,13 +2297,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="30"/>
@@ -2227,13 +2311,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="30"/>
@@ -2241,13 +2325,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="31" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B12" s="28">
         <v>99</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="30"/>
@@ -2271,10 +2355,10 @@
         <v>48</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="11"/>
@@ -2284,64 +2368,64 @@
         <v>48</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="C17" s="4" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>49</v>
@@ -2349,288 +2433,288 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>71</v>
+        <v>271</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>72</v>
+        <v>272</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>83</v>
+        <v>277</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>85</v>
+        <v>279</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>86</v>
+        <v>280</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>87</v>
+        <v>281</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -2638,10 +2722,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2649,10 +2733,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2660,10 +2744,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2671,10 +2755,10 @@
         <v>46</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2686,13 +2770,13 @@
         <v>47</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2700,13 +2784,13 @@
         <v>47</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2714,13 +2798,13 @@
         <v>47</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2728,13 +2812,13 @@
         <v>47</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2742,13 +2826,13 @@
         <v>47</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2756,13 +2840,13 @@
         <v>47</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2770,13 +2854,13 @@
         <v>47</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2784,13 +2868,13 @@
         <v>47</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2798,13 +2882,13 @@
         <v>47</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2812,13 +2896,13 @@
         <v>47</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2826,13 +2910,13 @@
         <v>47</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2840,13 +2924,13 @@
         <v>47</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2856,2303 +2940,2303 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B232" s="3">
         <v>101</v>
@@ -5161,12 +5245,12 @@
         <v>101</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B233" s="3">
         <v>102</v>
@@ -5175,12 +5259,12 @@
         <v>102</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B234" s="3">
         <v>103</v>
@@ -5189,12 +5273,12 @@
         <v>103</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B235" s="3">
         <v>104</v>
@@ -5203,12 +5287,12 @@
         <v>104</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B236" s="3">
         <v>105</v>
@@ -5217,12 +5301,12 @@
         <v>105</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B237" s="3">
         <v>106</v>
@@ -5231,12 +5315,12 @@
         <v>106</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B238" s="3">
         <v>107</v>
@@ -5245,12 +5329,12 @@
         <v>107</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B239" s="3">
         <v>108</v>
@@ -5259,12 +5343,12 @@
         <v>108</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B240" s="3">
         <v>109</v>
@@ -5273,12 +5357,12 @@
         <v>109</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B241" s="3">
         <v>110</v>
@@ -5287,12 +5371,12 @@
         <v>110</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B242" s="3">
         <v>111</v>
@@ -5301,12 +5385,12 @@
         <v>111</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B243" s="3">
         <v>112</v>
@@ -5315,12 +5399,12 @@
         <v>112</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B244" s="3">
         <v>113</v>
@@ -5329,12 +5413,12 @@
         <v>113</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B245" s="3">
         <v>114</v>
@@ -5343,12 +5427,12 @@
         <v>114</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B246" s="3">
         <v>115</v>
@@ -5357,12 +5441,12 @@
         <v>115</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B247" s="3">
         <v>116</v>
@@ -5371,12 +5455,12 @@
         <v>116</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B248" s="3">
         <v>117</v>
@@ -5385,12 +5469,12 @@
         <v>117</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B249" s="3">
         <v>118</v>
@@ -5399,12 +5483,12 @@
         <v>118</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B250" s="3">
         <v>119</v>
@@ -5413,12 +5497,12 @@
         <v>119</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B251" s="3">
         <v>120</v>
@@ -5427,12 +5511,12 @@
         <v>120</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B252" s="3">
         <v>121</v>
@@ -5441,12 +5525,12 @@
         <v>121</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B253" s="3">
         <v>122</v>
@@ -5455,12 +5539,12 @@
         <v>122</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B254" s="3">
         <v>123</v>
@@ -5469,12 +5553,12 @@
         <v>123</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B255" s="3">
         <v>124</v>
@@ -5483,12 +5567,12 @@
         <v>124</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
     </row>
     <row r="256" spans="1:7">
       <c r="A256" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B256" s="3">
         <v>125</v>
@@ -5497,12 +5581,12 @@
         <v>125</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
     </row>
     <row r="257" spans="1:7">
       <c r="A257" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B257" s="3">
         <v>126</v>
@@ -5511,12 +5595,12 @@
         <v>126</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
     </row>
     <row r="258" spans="1:7">
       <c r="A258" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B258" s="3">
         <v>127</v>
@@ -5525,12 +5609,12 @@
         <v>127</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="259" spans="1:7">
       <c r="A259" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B259" s="3">
         <v>128</v>
@@ -5539,12 +5623,12 @@
         <v>128</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="260" spans="1:7">
       <c r="A260" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B260" s="3">
         <v>129</v>
@@ -5553,12 +5637,12 @@
         <v>129</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B261" s="3">
         <v>130</v>
@@ -5567,12 +5651,12 @@
         <v>130</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B262" s="3">
         <v>131</v>
@@ -5581,12 +5665,12 @@
         <v>131</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B263" s="3">
         <v>132</v>
@@ -5595,12 +5679,12 @@
         <v>132</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B264" s="3">
         <v>133</v>
@@ -5609,12 +5693,12 @@
         <v>133</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B265" s="3">
         <v>134</v>
@@ -5623,12 +5707,12 @@
         <v>134</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B266" s="3">
         <v>135</v>
@@ -5637,12 +5721,12 @@
         <v>135</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B267" s="3">
         <v>136</v>
@@ -5651,12 +5735,12 @@
         <v>136</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B268" s="3">
         <v>137</v>
@@ -5665,12 +5749,12 @@
         <v>137</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B269" s="3">
         <v>138</v>
@@ -5679,12 +5763,12 @@
         <v>138</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B270" s="3">
         <v>139</v>
@@ -5693,12 +5777,12 @@
         <v>139</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B271" s="3">
         <v>140</v>
@@ -5707,12 +5791,12 @@
         <v>140</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B272" s="3">
         <v>141</v>
@@ -5721,12 +5805,12 @@
         <v>141</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B273" s="3">
         <v>142</v>
@@ -5735,12 +5819,12 @@
         <v>142</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B274" s="3">
         <v>143</v>
@@ -5749,12 +5833,12 @@
         <v>143</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B275" s="3">
         <v>144</v>
@@ -5763,12 +5847,12 @@
         <v>144</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B276" s="3">
         <v>145</v>
@@ -5777,12 +5861,12 @@
         <v>145</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B277" s="3">
         <v>146</v>
@@ -5791,12 +5875,12 @@
         <v>146</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B278" s="3">
         <v>147</v>
@@ -5805,12 +5889,12 @@
         <v>147</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B279" s="3">
         <v>148</v>
@@ -5819,12 +5903,12 @@
         <v>148</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B280" s="3">
         <v>149</v>
@@ -5833,12 +5917,12 @@
         <v>149</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B281" s="3">
         <v>150</v>
@@ -5847,12 +5931,12 @@
         <v>150</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B282" s="3">
         <v>151</v>
@@ -5861,12 +5945,12 @@
         <v>151</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B283" s="3">
         <v>152</v>
@@ -5875,12 +5959,12 @@
         <v>152</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B284" s="3">
         <v>153</v>
@@ -5889,12 +5973,12 @@
         <v>153</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B285" s="3">
         <v>154</v>
@@ -5903,12 +5987,12 @@
         <v>154</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B286" s="3">
         <v>155</v>
@@ -5917,12 +6001,12 @@
         <v>155</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B287" s="3">
         <v>156</v>
@@ -5931,12 +6015,12 @@
         <v>156</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B288" s="3">
         <v>157</v>
@@ -5945,12 +6029,12 @@
         <v>157</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="289" spans="1:7">
       <c r="A289" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B289" s="3">
         <v>158</v>
@@ -5959,12 +6043,12 @@
         <v>158</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B290" s="3">
         <v>159</v>
@@ -5973,12 +6057,12 @@
         <v>159</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B291" s="3">
         <v>160</v>
@@ -5987,12 +6071,12 @@
         <v>160</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B292" s="3">
         <v>161</v>
@@ -6001,12 +6085,12 @@
         <v>161</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B293" s="3">
         <v>162</v>
@@ -6015,12 +6099,12 @@
         <v>162</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B294" s="3">
         <v>163</v>
@@ -6029,12 +6113,12 @@
         <v>163</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B295" s="3">
         <v>164</v>
@@ -6043,12 +6127,12 @@
         <v>164</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B296" s="3">
         <v>165</v>
@@ -6057,12 +6141,12 @@
         <v>165</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B297" s="3">
         <v>166</v>
@@ -6071,12 +6155,12 @@
         <v>166</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B298" s="3">
         <v>167</v>
@@ -6085,12 +6169,12 @@
         <v>167</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B299" s="3">
         <v>168</v>
@@ -6099,12 +6183,12 @@
         <v>168</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B300" s="3">
         <v>169</v>
@@ -6113,12 +6197,12 @@
         <v>169</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B301" s="3">
         <v>170</v>
@@ -6127,12 +6211,12 @@
         <v>170</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B302" s="3">
         <v>171</v>
@@ -6141,12 +6225,12 @@
         <v>171</v>
       </c>
       <c r="G302" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B303" s="3">
         <v>172</v>
@@ -6155,12 +6239,12 @@
         <v>172</v>
       </c>
       <c r="G303" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B304" s="3">
         <v>173</v>
@@ -6169,12 +6253,12 @@
         <v>173</v>
       </c>
       <c r="G304" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B305" s="3">
         <v>174</v>
@@ -6183,12 +6267,12 @@
         <v>174</v>
       </c>
       <c r="G305" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B306" s="3">
         <v>175</v>
@@ -6197,12 +6281,12 @@
         <v>175</v>
       </c>
       <c r="G306" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
     </row>
     <row r="307" spans="1:7">
       <c r="A307" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B307" s="3">
         <v>176</v>
@@ -6211,12 +6295,12 @@
         <v>176</v>
       </c>
       <c r="G307" s="3" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
     </row>
     <row r="308" spans="1:7">
       <c r="A308" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B308" s="3">
         <v>177</v>
@@ -6225,12 +6309,12 @@
         <v>177</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
     </row>
     <row r="309" spans="1:7">
       <c r="A309" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B309" s="3">
         <v>178</v>
@@ -6239,12 +6323,12 @@
         <v>178</v>
       </c>
       <c r="G309" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B310" s="3">
         <v>179</v>
@@ -6253,12 +6337,12 @@
         <v>179</v>
       </c>
       <c r="G310" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="311" spans="1:7">
       <c r="A311" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B311" s="3">
         <v>180</v>
@@ -6267,12 +6351,12 @@
         <v>180</v>
       </c>
       <c r="G311" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="312" spans="1:7">
       <c r="A312" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B312" s="3">
         <v>181</v>
@@ -6281,12 +6365,12 @@
         <v>181</v>
       </c>
       <c r="G312" s="3" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
     </row>
     <row r="313" spans="1:7">
       <c r="A313" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B313" s="3">
         <v>182</v>
@@ -6295,12 +6379,12 @@
         <v>182</v>
       </c>
       <c r="G313" s="3" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
     </row>
     <row r="314" spans="1:7">
       <c r="A314" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B314" s="3">
         <v>183</v>
@@ -6309,12 +6393,12 @@
         <v>183</v>
       </c>
       <c r="G314" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B315" s="3">
         <v>184</v>
@@ -6323,12 +6407,12 @@
         <v>184</v>
       </c>
       <c r="G315" s="3" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
     </row>
     <row r="316" spans="1:7">
       <c r="A316" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B316" s="3">
         <v>185</v>
@@ -6337,12 +6421,12 @@
         <v>185</v>
       </c>
       <c r="G316" s="3" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B317" s="3">
         <v>186</v>
@@ -6351,12 +6435,12 @@
         <v>186</v>
       </c>
       <c r="G317" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="318" spans="1:7">
       <c r="A318" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B318" s="3">
         <v>187</v>
@@ -6365,12 +6449,12 @@
         <v>187</v>
       </c>
       <c r="G318" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="319" spans="1:7">
       <c r="A319" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B319" s="3">
         <v>188</v>
@@ -6379,12 +6463,12 @@
         <v>188</v>
       </c>
       <c r="G319" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="320" spans="1:7">
       <c r="A320" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B320" s="3">
         <v>189</v>
@@ -6393,12 +6477,12 @@
         <v>189</v>
       </c>
       <c r="G320" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="321" spans="1:7">
       <c r="A321" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B321" s="3">
         <v>190</v>
@@ -6407,12 +6491,12 @@
         <v>190</v>
       </c>
       <c r="G321" s="3" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
     </row>
     <row r="322" spans="1:7">
       <c r="A322" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B322" s="3">
         <v>191</v>
@@ -6421,12 +6505,12 @@
         <v>191</v>
       </c>
       <c r="G322" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="323" spans="1:7">
       <c r="A323" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B323" s="3">
         <v>192</v>
@@ -6435,12 +6519,12 @@
         <v>192</v>
       </c>
       <c r="G323" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="324" spans="1:7">
       <c r="A324" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B324" s="3">
         <v>193</v>
@@ -6449,12 +6533,12 @@
         <v>193</v>
       </c>
       <c r="G324" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="325" spans="1:7">
       <c r="A325" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B325" s="3">
         <v>194</v>
@@ -6463,12 +6547,12 @@
         <v>194</v>
       </c>
       <c r="G325" s="3" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
     </row>
     <row r="326" spans="1:7">
       <c r="A326" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B326" s="3">
         <v>195</v>
@@ -6477,12 +6561,12 @@
         <v>195</v>
       </c>
       <c r="G326" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="327" spans="1:7">
       <c r="A327" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B327" s="3">
         <v>196</v>
@@ -6491,12 +6575,12 @@
         <v>196</v>
       </c>
       <c r="G327" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="328" spans="1:7">
       <c r="A328" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B328" s="3">
         <v>197</v>
@@ -6505,12 +6589,12 @@
         <v>197</v>
       </c>
       <c r="G328" s="3" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
     </row>
     <row r="329" spans="1:7">
       <c r="A329" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B329" s="3">
         <v>198</v>
@@ -6519,12 +6603,12 @@
         <v>198</v>
       </c>
       <c r="G329" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
     </row>
     <row r="330" spans="1:7">
       <c r="A330" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B330" s="3">
         <v>199</v>
@@ -6533,12 +6617,12 @@
         <v>199</v>
       </c>
       <c r="G330" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="331" spans="1:7">
       <c r="A331" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B331" s="3">
         <v>200</v>
@@ -6547,12 +6631,12 @@
         <v>200</v>
       </c>
       <c r="G331" s="3" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
     <row r="333" spans="1:7">
       <c r="A333" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B333" s="3">
         <v>101</v>
@@ -6562,15 +6646,15 @@
         <v>101 (Mvog-Ada)</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B334" s="3">
         <v>102</v>
@@ -6580,15 +6664,15 @@
         <v>102 (Karen)</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="335" spans="1:7">
       <c r="A335" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B335" s="3">
         <v>103</v>
@@ -6598,15 +6682,15 @@
         <v>103 (Arada)</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="G335" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
     </row>
     <row r="336" spans="1:7">
       <c r="A336" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B336" s="3">
         <v>104</v>
@@ -6616,15 +6700,15 @@
         <v>104 (Soweto)</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="G336" s="3" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="337" spans="1:7">
       <c r="A337" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B337" s="3">
         <v>105</v>
@@ -6634,15 +6718,15 @@
         <v>105 (Talangaï)</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="G337" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="338" spans="1:7">
       <c r="A338" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B338" s="3">
         <v>106</v>
@@ -6652,15 +6736,15 @@
         <v>106 (Osu)</v>
       </c>
       <c r="F338" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G338" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B339" s="3">
         <v>107</v>
@@ -6670,15 +6754,15 @@
         <v>107 (Yeka)</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="G339" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B340" s="3">
         <v>108</v>
@@ -6688,15 +6772,15 @@
         <v>108 (Soweto)</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="G340" s="3" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B341" s="3">
         <v>109</v>
@@ -6706,15 +6790,15 @@
         <v>109 (Osu)</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G341" s="3" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B342" s="3">
         <v>110</v>
@@ -6724,15 +6808,15 @@
         <v>110 (Bole)</v>
       </c>
       <c r="F342" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G342" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B343" s="3">
         <v>111</v>
@@ -6742,15 +6826,15 @@
         <v>111 (Karen)</v>
       </c>
       <c r="F343" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="G343" s="3" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B344" s="3">
         <v>112</v>
@@ -6760,15 +6844,15 @@
         <v>112 (Poto-Poto)</v>
       </c>
       <c r="F344" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G344" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B345" s="3">
         <v>113</v>
@@ -6778,15 +6862,15 @@
         <v>113 (Randburg)</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="G345" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B346" s="3">
         <v>114</v>
@@ -6796,15 +6880,15 @@
         <v>114 (Labadi)</v>
       </c>
       <c r="F346" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="G346" s="3" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B347" s="3">
         <v>115</v>
@@ -6814,15 +6898,15 @@
         <v>115 (Essos)</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="G347" s="3" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
     </row>
     <row r="348" spans="1:7">
       <c r="A348" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B348" s="3">
         <v>116</v>
@@ -6832,15 +6916,15 @@
         <v>116 (Arada)</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="G348" s="3" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="349" spans="1:7">
       <c r="A349" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B349" s="3">
         <v>117</v>
@@ -6850,15 +6934,15 @@
         <v>117 (Poto-Poto)</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G349" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B350" s="3">
         <v>118</v>
@@ -6868,15 +6952,15 @@
         <v>118 (Ikeja)</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="G350" s="3" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B351" s="3">
         <v>119</v>
@@ -6886,15 +6970,15 @@
         <v>119 (Gombe)</v>
       </c>
       <c r="F351" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="G351" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="352" spans="1:7">
       <c r="A352" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B352" s="3">
         <v>120</v>
@@ -6904,15 +6988,15 @@
         <v>120 (Nakawa)</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="G352" s="3" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B353" s="3">
         <v>121</v>
@@ -6922,15 +7006,15 @@
         <v>121 (Bacongo)</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="G353" s="3" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
     </row>
     <row r="354" spans="1:7">
       <c r="A354" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B354" s="3">
         <v>122</v>
@@ -6940,15 +7024,15 @@
         <v>122 (Poto-Poto)</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G354" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
     </row>
     <row r="355" spans="1:7">
       <c r="A355" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B355" s="3">
         <v>123</v>
@@ -6958,15 +7042,15 @@
         <v>123 (Surulere)</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="G355" s="3" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
     </row>
     <row r="356" spans="1:7">
       <c r="A356" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B356" s="3">
         <v>124</v>
@@ -6976,15 +7060,15 @@
         <v>124 (Nakawa)</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="G356" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
     </row>
     <row r="357" spans="1:7">
       <c r="A357" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B357" s="3">
         <v>125</v>
@@ -6994,15 +7078,15 @@
         <v>125 (Ikeja)</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="G357" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
     </row>
     <row r="358" spans="1:7">
       <c r="A358" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B358" s="3">
         <v>126</v>
@@ -7012,15 +7096,15 @@
         <v>126 (Talangaï)</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="G358" s="3" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
     </row>
     <row r="359" spans="1:7">
       <c r="A359" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B359" s="3">
         <v>127</v>
@@ -7030,15 +7114,15 @@
         <v>127 (Chilenje)</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="G359" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="360" spans="1:7">
       <c r="A360" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B360" s="3">
         <v>128</v>
@@ -7048,15 +7132,15 @@
         <v>128 (Poto-Poto)</v>
       </c>
       <c r="F360" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G360" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="361" spans="1:7">
       <c r="A361" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B361" s="3">
         <v>129</v>
@@ -7066,15 +7150,15 @@
         <v>129 (Borrowdale)</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="G361" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="362" spans="1:7">
       <c r="A362" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B362" s="3">
         <v>130</v>
@@ -7084,15 +7168,15 @@
         <v>130 (Yaba)</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G362" s="3" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
     </row>
     <row r="363" spans="1:7">
       <c r="A363" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B363" s="3">
         <v>131</v>
@@ -7102,15 +7186,15 @@
         <v>131 (Mvog-Ada)</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="G363" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="364" spans="1:7">
       <c r="A364" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B364" s="3">
         <v>132</v>
@@ -7120,15 +7204,15 @@
         <v>132 (Mvog-Ada)</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="G364" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
     </row>
     <row r="365" spans="1:7">
       <c r="A365" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B365" s="3">
         <v>133</v>
@@ -7138,15 +7222,15 @@
         <v>133 (Labadi)</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="G365" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B366" s="3">
         <v>134</v>
@@ -7156,15 +7240,15 @@
         <v>134 (Poto-Poto)</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G366" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B367" s="3">
         <v>135</v>
@@ -7174,15 +7258,15 @@
         <v>135 (Madina)</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G367" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B368" s="3">
         <v>136</v>
@@ -7192,15 +7276,15 @@
         <v>136 (Labadi)</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="G368" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B369" s="3">
         <v>137</v>
@@ -7210,15 +7294,15 @@
         <v>137 (Randburg)</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="G369" s="3" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B370" s="3">
         <v>138</v>
@@ -7228,15 +7312,15 @@
         <v>138 (Bole)</v>
       </c>
       <c r="F370" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G370" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B371" s="3">
         <v>139</v>
@@ -7246,15 +7330,15 @@
         <v>139 (Ikeja)</v>
       </c>
       <c r="F371" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="G371" s="3" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B372" s="3">
         <v>140</v>
@@ -7264,15 +7348,15 @@
         <v>140 (Talangaï)</v>
       </c>
       <c r="F372" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="G372" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B373" s="3">
         <v>141</v>
@@ -7282,15 +7366,15 @@
         <v>141 (Gombe)</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="G373" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B374" s="3">
         <v>142</v>
@@ -7300,15 +7384,15 @@
         <v>142 (Medina)</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="G374" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B375" s="3">
         <v>143</v>
@@ -7318,15 +7402,15 @@
         <v>143 (Medina)</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="G375" s="3" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B376" s="3">
         <v>144</v>
@@ -7336,15 +7420,15 @@
         <v>144 (Randburg)</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="G376" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B377" s="3">
         <v>145</v>
@@ -7354,15 +7438,15 @@
         <v>145 (Sandton)</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="G377" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
     </row>
     <row r="378" spans="1:7">
       <c r="A378" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B378" s="3">
         <v>146</v>
@@ -7372,15 +7456,15 @@
         <v>146 (Yeka)</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="G378" s="3" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B379" s="3">
         <v>147</v>
@@ -7390,15 +7474,15 @@
         <v>147 (Makindye)</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="G379" s="3" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B380" s="3">
         <v>148</v>
@@ -7408,15 +7492,15 @@
         <v>148 (Gombe)</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="G380" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B381" s="3">
         <v>149</v>
@@ -7426,15 +7510,15 @@
         <v>149 (Yeka)</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="G381" s="3" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B382" s="3">
         <v>150</v>
@@ -7444,15 +7528,15 @@
         <v>150 (Ikeja)</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="G382" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B383" s="3">
         <v>151</v>
@@ -7462,15 +7546,15 @@
         <v>151 (Poto-Poto)</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G383" s="3" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B384" s="3">
         <v>152</v>
@@ -7480,15 +7564,15 @@
         <v>152 (Bacongo)</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="G384" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B385" s="3">
         <v>153</v>
@@ -7498,15 +7582,15 @@
         <v>153 (Gombe)</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="G385" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B386" s="3">
         <v>154</v>
@@ -7516,15 +7600,15 @@
         <v>154 (Bole)</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G386" s="3" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B387" s="3">
         <v>155</v>
@@ -7534,15 +7618,15 @@
         <v>155 (Talangaï)</v>
       </c>
       <c r="F387" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="G387" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B388" s="3">
         <v>156</v>
@@ -7552,15 +7636,15 @@
         <v>156 (Matero)</v>
       </c>
       <c r="F388" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="G388" s="3" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
     </row>
     <row r="389" spans="1:7">
       <c r="A389" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B389" s="3">
         <v>157</v>
@@ -7570,15 +7654,15 @@
         <v>157 (Yaba)</v>
       </c>
       <c r="F389" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G389" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B390" s="3">
         <v>158</v>
@@ -7588,15 +7672,15 @@
         <v>158 (Matero)</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="G390" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B391" s="3">
         <v>159</v>
@@ -7606,15 +7690,15 @@
         <v>159 (Plateau)</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="G391" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="392" spans="1:7">
       <c r="A392" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B392" s="3">
         <v>160</v>
@@ -7624,15 +7708,15 @@
         <v>160 (Karen)</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="G392" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="393" spans="1:7">
       <c r="A393" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B393" s="3">
         <v>161</v>
@@ -7642,15 +7726,15 @@
         <v>161 (Pikine)</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="G393" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
     </row>
     <row r="394" spans="1:7">
       <c r="A394" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B394" s="3">
         <v>162</v>
@@ -7660,15 +7744,15 @@
         <v>162 (Matero)</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="G394" s="3" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
     </row>
     <row r="395" spans="1:7">
       <c r="A395" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B395" s="3">
         <v>163</v>
@@ -7678,15 +7762,15 @@
         <v>163 (Madina)</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G395" s="3" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
     </row>
     <row r="396" spans="1:7">
       <c r="A396" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B396" s="3">
         <v>164</v>
@@ -7696,15 +7780,15 @@
         <v>164 (Surulere)</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="G396" s="3" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
     </row>
     <row r="397" spans="1:7">
       <c r="A397" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B397" s="3">
         <v>165</v>
@@ -7714,15 +7798,15 @@
         <v>165 (Osu)</v>
       </c>
       <c r="F397" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G397" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
     </row>
     <row r="398" spans="1:7">
       <c r="A398" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B398" s="3">
         <v>166</v>
@@ -7732,15 +7816,15 @@
         <v>166 (Pikine)</v>
       </c>
       <c r="F398" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="G398" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="399" spans="1:7">
       <c r="A399" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B399" s="3">
         <v>167</v>
@@ -7750,15 +7834,15 @@
         <v>167 (Kibera)</v>
       </c>
       <c r="F399" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="G399" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
     </row>
     <row r="400" spans="1:7">
       <c r="A400" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B400" s="3">
         <v>168</v>
@@ -7768,15 +7852,15 @@
         <v>168 (Nakawa)</v>
       </c>
       <c r="F400" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="G400" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="401" spans="1:7">
       <c r="A401" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B401" s="3">
         <v>169</v>
@@ -7786,15 +7870,15 @@
         <v>169 (Gombe)</v>
       </c>
       <c r="F401" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="G401" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
     </row>
     <row r="402" spans="1:7">
       <c r="A402" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B402" s="3">
         <v>170</v>
@@ -7804,15 +7888,15 @@
         <v>170 (Makindye)</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="G402" s="3" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
     </row>
     <row r="403" spans="1:7">
       <c r="A403" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B403" s="3">
         <v>171</v>
@@ -7822,15 +7906,15 @@
         <v>171 (Mvog-Ada)</v>
       </c>
       <c r="F403" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="G403" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="404" spans="1:7">
       <c r="A404" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B404" s="3">
         <v>172</v>
@@ -7840,15 +7924,15 @@
         <v>172 (Kabulonga)</v>
       </c>
       <c r="F404" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="G404" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="405" spans="1:7">
       <c r="A405" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B405" s="3">
         <v>173</v>
@@ -7858,15 +7942,15 @@
         <v>173 (Matero)</v>
       </c>
       <c r="F405" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="G405" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="406" spans="1:7">
       <c r="A406" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B406" s="3">
         <v>174</v>
@@ -7876,15 +7960,15 @@
         <v>174 (Essos)</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="G406" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="407" spans="1:7">
       <c r="A407" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B407" s="3">
         <v>175</v>
@@ -7894,15 +7978,15 @@
         <v>175 (Talangaï)</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="G407" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
     </row>
     <row r="408" spans="1:7">
       <c r="A408" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B408" s="3">
         <v>176</v>
@@ -7912,15 +7996,15 @@
         <v>176 (Mvog-Ada)</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="G408" s="3" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
     </row>
     <row r="409" spans="1:7">
       <c r="A409" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B409" s="3">
         <v>177</v>
@@ -7930,15 +8014,15 @@
         <v>177 (Essos)</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="G409" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
     </row>
     <row r="410" spans="1:7">
       <c r="A410" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B410" s="3">
         <v>178</v>
@@ -7948,15 +8032,15 @@
         <v>178 (Medina)</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="G410" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="411" spans="1:7">
       <c r="A411" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B411" s="3">
         <v>179</v>
@@ -7966,15 +8050,15 @@
         <v>179 (Ikeja)</v>
       </c>
       <c r="F411" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="G411" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="412" spans="1:7">
       <c r="A412" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B412" s="3">
         <v>180</v>
@@ -7984,15 +8068,15 @@
         <v>180 (Karen)</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="G412" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="413" spans="1:7">
       <c r="A413" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B413" s="3">
         <v>181</v>
@@ -8002,15 +8086,15 @@
         <v>181 (Yaba)</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G413" s="3" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
     </row>
     <row r="414" spans="1:7">
       <c r="A414" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B414" s="3">
         <v>182</v>
@@ -8020,15 +8104,15 @@
         <v>182 (Randburg)</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="G414" s="3" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
     </row>
     <row r="415" spans="1:7">
       <c r="A415" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B415" s="3">
         <v>183</v>
@@ -8038,15 +8122,15 @@
         <v>183 (Bole)</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G415" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
     </row>
     <row r="416" spans="1:7">
       <c r="A416" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B416" s="3">
         <v>184</v>
@@ -8056,15 +8140,15 @@
         <v>184 (Yaba)</v>
       </c>
       <c r="F416" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G416" s="3" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
     </row>
     <row r="417" spans="1:7">
       <c r="A417" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B417" s="3">
         <v>185</v>
@@ -8074,15 +8158,15 @@
         <v>185 (Pikine)</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="G417" s="3" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
     </row>
     <row r="418" spans="1:7">
       <c r="A418" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B418" s="3">
         <v>186</v>
@@ -8092,15 +8176,15 @@
         <v>186 (Talangaï)</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="G418" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="419" spans="1:7">
       <c r="A419" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B419" s="3">
         <v>187</v>
@@ -8110,15 +8194,15 @@
         <v>187 (Karen)</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="G419" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="420" spans="1:7">
       <c r="A420" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B420" s="3">
         <v>188</v>
@@ -8128,15 +8212,15 @@
         <v>188 (Madina)</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G420" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="421" spans="1:7">
       <c r="A421" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B421" s="3">
         <v>189</v>
@@ -8146,15 +8230,15 @@
         <v>189 (Kawempe)</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="G421" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="422" spans="1:7">
       <c r="A422" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B422" s="3">
         <v>190</v>
@@ -8164,15 +8248,15 @@
         <v>190 (Sandton)</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="G422" s="3" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
     </row>
     <row r="423" spans="1:7">
       <c r="A423" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B423" s="3">
         <v>191</v>
@@ -8182,15 +8266,15 @@
         <v>191 (Matete)</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="G423" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="424" spans="1:7">
       <c r="A424" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B424" s="3">
         <v>192</v>
@@ -8200,15 +8284,15 @@
         <v>192 (Poto-Poto)</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G424" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="425" spans="1:7">
       <c r="A425" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B425" s="3">
         <v>193</v>
@@ -8218,15 +8302,15 @@
         <v>193 (Kabulonga)</v>
       </c>
       <c r="F425" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="G425" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="426" spans="1:7">
       <c r="A426" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B426" s="3">
         <v>194</v>
@@ -8236,15 +8320,15 @@
         <v>194 (Surulere)</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="G426" s="3" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
     </row>
     <row r="427" spans="1:7">
       <c r="A427" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B427" s="3">
         <v>195</v>
@@ -8254,15 +8338,15 @@
         <v>195 (Matero)</v>
       </c>
       <c r="F427" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="G427" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="428" spans="1:7">
       <c r="A428" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B428" s="3">
         <v>196</v>
@@ -8272,15 +8356,15 @@
         <v>196 (Highfield)</v>
       </c>
       <c r="F428" s="3" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="G428" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="429" spans="1:7">
       <c r="A429" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B429" s="3">
         <v>197</v>
@@ -8290,15 +8374,15 @@
         <v>197 (Bole)</v>
       </c>
       <c r="F429" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G429" s="3" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
     </row>
     <row r="430" spans="1:7">
       <c r="A430" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B430" s="3">
         <v>198</v>
@@ -8308,15 +8392,15 @@
         <v>198 (Pikine)</v>
       </c>
       <c r="F430" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="G430" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
     </row>
     <row r="431" spans="1:7">
       <c r="A431" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B431" s="3">
         <v>199</v>
@@ -8326,15 +8410,15 @@
         <v>199 (Ikeja)</v>
       </c>
       <c r="F431" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="G431" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B432" s="3">
         <v>200</v>
@@ -8344,10 +8428,10 @@
         <v>200 (Bacongo)</v>
       </c>
       <c r="F432" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="G432" s="3" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -8373,27 +8457,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>

--- a/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_1_river_assess.xlsx
+++ b/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_1_river_assess.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\ONCHO\ento\river prospection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA08AC1C-19F2-463A-AE55-0DBE0CB9476E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FFD7E3-0EA6-462A-852A-BF2C2C26A01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="314">
   <si>
     <t>type</t>
   </si>
@@ -886,9 +886,6 @@
     <t>Border.site.with.Zanzibar</t>
   </si>
   <si>
-    <t>demo_oncho_priv_prosp_9999_1_river_asses</t>
-  </si>
-  <si>
     <t>s_densite</t>
   </si>
   <si>
@@ -923,6 +920,63 @@
   </si>
   <si>
     <t>Please enter a correct pH</t>
+  </si>
+  <si>
+    <t>demo_oncho_priv_prosp_9999_1_river_asses_2</t>
+  </si>
+  <si>
+    <t>Inspection Time</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>Is site suitable for black fly breeding. </t>
+  </si>
+  <si>
+    <t>Does the site has evidence of larvae</t>
+  </si>
+  <si>
+    <t>Abundance - How many larvae where found?    </t>
+  </si>
+  <si>
+    <t>s_inspection_time</t>
+  </si>
+  <si>
+    <t>s_site_suitability</t>
+  </si>
+  <si>
+    <t>s_larvae_evidence</t>
+  </si>
+  <si>
+    <t>s_abundance</t>
+  </si>
+  <si>
+    <t>select_one yes_no</t>
+  </si>
+  <si>
+    <t>select_one abundance</t>
+  </si>
+  <si>
+    <t>abundance</t>
+  </si>
+  <si>
+    <t>1 – 10</t>
+  </si>
+  <si>
+    <t>11 – 50</t>
+  </si>
+  <si>
+    <t>51 – 100</t>
+  </si>
+  <si>
+    <t>101 – 150</t>
+  </si>
+  <si>
+    <t>151 – 200</t>
+  </si>
+  <si>
+    <t>More than 201</t>
   </si>
 </sst>
 </file>
@@ -981,7 +1035,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -997,6 +1051,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1054,7 +1114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1125,6 +1185,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1407,7 +1471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26" style="3" customWidth="1"/>
@@ -1789,13 +1853,13 @@
     </row>
     <row r="15" spans="1:13" s="4" customFormat="1">
       <c r="A15" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="21"/>
@@ -1812,21 +1876,21 @@
     </row>
     <row r="16" spans="1:13" s="4" customFormat="1">
       <c r="A16" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="21"/>
       <c r="F16" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="G16" s="23" t="s">
         <v>292</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>293</v>
       </c>
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
@@ -1842,148 +1906,154 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>286</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>287</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="21"/>
       <c r="F17" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="G17" s="23" t="s">
         <v>294</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>295</v>
       </c>
       <c r="H17" s="22"/>
       <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
+      <c r="J17" s="22" t="s">
+        <v>11</v>
+      </c>
       <c r="K17" s="22"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="21" t="s">
+    <row r="18" spans="1:13" s="4" customFormat="1">
+      <c r="A18" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="D18" s="23"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="21" t="s">
+      <c r="K18" s="22"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+    </row>
+    <row r="19" spans="1:13" s="4" customFormat="1" ht="31.5">
+      <c r="A19" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D19" s="23"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="21" t="s">
+      <c r="K19" s="22"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+    </row>
+    <row r="20" spans="1:13" s="4" customFormat="1" ht="31.5">
+      <c r="A20" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+    </row>
+    <row r="21" spans="1:13" s="4" customFormat="1" ht="31.5">
+      <c r="A21" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="D21" s="23"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="22"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="26" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="27"/>
+        <v>103</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>269</v>
+      </c>
       <c r="E22" s="26"/>
       <c r="F22" s="26"/>
       <c r="G22" s="27"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="21"/>
+      <c r="J22" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
       <c r="M22" s="26"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="26" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="26"/>
@@ -1991,155 +2061,243 @@
       <c r="G23" s="27"/>
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
-      <c r="J23" s="21"/>
+      <c r="J23" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="K23" s="26"/>
       <c r="L23" s="26"/>
       <c r="M23" s="26"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="26" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="26"/>
       <c r="F24" s="26"/>
       <c r="G24" s="27"/>
-      <c r="H24" s="26" t="s">
-        <v>34</v>
-      </c>
+      <c r="H24" s="26"/>
       <c r="I24" s="26"/>
-      <c r="J24" s="21"/>
+      <c r="J24" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
       <c r="M24" s="26"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="26" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>270</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D25" s="27"/>
       <c r="E25" s="26"/>
       <c r="F25" s="26"/>
       <c r="G25" s="27"/>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
-      <c r="J25" s="21" t="s">
-        <v>11</v>
-      </c>
+      <c r="J25" s="21"/>
       <c r="K25" s="26"/>
       <c r="L25" s="26"/>
       <c r="M25" s="26"/>
     </row>
-    <row r="26" spans="1:13" s="4" customFormat="1">
-      <c r="A26" s="21" t="s">
+    <row r="26" spans="1:13">
+      <c r="A26" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="27"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="26"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+    </row>
+    <row r="30" spans="1:13" s="4" customFormat="1">
+      <c r="A30" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B30" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C30" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-    </row>
-    <row r="27" spans="1:13" s="4" customFormat="1">
-      <c r="A27" s="21" t="s">
+      <c r="D30" s="23"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+    </row>
+    <row r="31" spans="1:13" s="4" customFormat="1">
+      <c r="A31" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B31" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C31" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="26" t="s">
+      <c r="D31" s="23"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="I27" s="21"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-    </row>
-    <row r="28" spans="1:13" s="4" customFormat="1">
-      <c r="A28" s="21" t="s">
+      <c r="I31" s="21"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+    </row>
+    <row r="32" spans="1:13" s="4" customFormat="1">
+      <c r="A32" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B32" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-    </row>
-    <row r="29" spans="1:13" s="4" customFormat="1">
-      <c r="A29" s="21" t="s">
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+    </row>
+    <row r="33" spans="1:13" s="4" customFormat="1">
+      <c r="A33" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B33" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-    </row>
-    <row r="30" spans="1:13" s="4" customFormat="1">
-      <c r="B30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:13" s="4" customFormat="1">
-      <c r="B31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="1:13" s="4" customFormat="1">
-      <c r="B32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+    </row>
+    <row r="34" spans="1:13" s="4" customFormat="1">
+      <c r="B34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" s="4" customFormat="1">
+      <c r="B35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:13" s="4" customFormat="1">
+      <c r="B36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="G36" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2149,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G432"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="16.375" style="3" customWidth="1"/>
@@ -2717,150 +2875,132 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>118</v>
+    <row r="47" spans="1:3" customFormat="1">
+      <c r="A47" t="s">
+        <v>307</v>
+      </c>
+      <c r="B47" t="s">
+        <v>308</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" customFormat="1">
+      <c r="A48" t="s">
+        <v>307</v>
+      </c>
+      <c r="B48" t="s">
+        <v>309</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" customFormat="1">
+      <c r="A49" t="s">
+        <v>307</v>
+      </c>
+      <c r="B49" t="s">
+        <v>310</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" customFormat="1">
+      <c r="A50" t="s">
+        <v>307</v>
+      </c>
+      <c r="B50" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" customFormat="1">
+      <c r="A51" t="s">
+        <v>307</v>
+      </c>
+      <c r="B51" t="s">
+        <v>312</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" customFormat="1">
+      <c r="A52" t="s">
+        <v>307</v>
+      </c>
+      <c r="B52" t="s">
+        <v>313</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D54" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>119</v>
-      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2868,13 +3008,13 @@
         <v>47</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2882,13 +3022,13 @@
         <v>47</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2896,13 +3036,13 @@
         <v>47</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2910,13 +3050,13 @@
         <v>47</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2924,116 +3064,116 @@
         <v>47</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
+      <c r="A65" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>131</v>
+        <v>47</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>131</v>
+        <v>47</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>131</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>125</v>
+        <v>47</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>125</v>
+        <v>47</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
         <v>117</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3041,13 +3181,13 @@
         <v>117</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3055,13 +3195,13 @@
         <v>117</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3069,13 +3209,13 @@
         <v>117</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3083,13 +3223,13 @@
         <v>117</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3097,13 +3237,13 @@
         <v>117</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3111,13 +3251,13 @@
         <v>117</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3125,13 +3265,13 @@
         <v>117</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3139,13 +3279,13 @@
         <v>117</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3153,13 +3293,13 @@
         <v>117</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3167,13 +3307,13 @@
         <v>117</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3181,13 +3321,13 @@
         <v>117</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3195,13 +3335,13 @@
         <v>117</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3209,13 +3349,13 @@
         <v>117</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3223,13 +3363,13 @@
         <v>117</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3237,13 +3377,13 @@
         <v>117</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3251,13 +3391,13 @@
         <v>117</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3265,13 +3405,13 @@
         <v>117</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3279,13 +3419,13 @@
         <v>117</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3293,13 +3433,13 @@
         <v>117</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3307,13 +3447,13 @@
         <v>117</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3321,13 +3461,13 @@
         <v>117</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3335,13 +3475,13 @@
         <v>117</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3349,13 +3489,13 @@
         <v>117</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3363,13 +3503,13 @@
         <v>117</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3377,97 +3517,97 @@
         <v>117</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="3" t="s">
-        <v>229</v>
+        <v>117</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>137</v>
+        <v>161</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="3" t="s">
-        <v>229</v>
+        <v>117</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>137</v>
+        <v>162</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="3" t="s">
-        <v>229</v>
+        <v>117</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>140</v>
+        <v>163</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="3" t="s">
-        <v>229</v>
+        <v>117</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>140</v>
+        <v>164</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="3" t="s">
-        <v>229</v>
+        <v>117</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>138</v>
+        <v>165</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3475,13 +3615,13 @@
         <v>229</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3489,13 +3629,13 @@
         <v>229</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3503,13 +3643,13 @@
         <v>229</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3517,13 +3657,13 @@
         <v>229</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3531,13 +3671,13 @@
         <v>229</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3545,13 +3685,13 @@
         <v>229</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3559,13 +3699,13 @@
         <v>229</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3573,13 +3713,13 @@
         <v>229</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3587,13 +3727,13 @@
         <v>229</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3601,13 +3741,13 @@
         <v>229</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3615,13 +3755,13 @@
         <v>229</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3629,13 +3769,13 @@
         <v>229</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3643,13 +3783,13 @@
         <v>229</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3657,13 +3797,13 @@
         <v>229</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3671,13 +3811,13 @@
         <v>229</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3685,13 +3825,13 @@
         <v>229</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3699,13 +3839,13 @@
         <v>229</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3713,13 +3853,13 @@
         <v>229</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3727,13 +3867,13 @@
         <v>229</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3741,13 +3881,13 @@
         <v>229</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3761,7 +3901,7 @@
         <v>186</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3769,13 +3909,13 @@
         <v>229</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3783,13 +3923,13 @@
         <v>229</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3797,13 +3937,13 @@
         <v>229</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3811,13 +3951,13 @@
         <v>229</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3825,13 +3965,13 @@
         <v>229</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3839,13 +3979,13 @@
         <v>229</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3853,13 +3993,13 @@
         <v>229</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3867,13 +4007,13 @@
         <v>229</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3881,13 +4021,13 @@
         <v>229</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3895,13 +4035,13 @@
         <v>229</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3909,13 +4049,13 @@
         <v>229</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3923,13 +4063,13 @@
         <v>229</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3937,13 +4077,13 @@
         <v>229</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3951,13 +4091,13 @@
         <v>229</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3965,13 +4105,13 @@
         <v>229</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3979,13 +4119,13 @@
         <v>229</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3993,13 +4133,13 @@
         <v>229</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4007,13 +4147,13 @@
         <v>229</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4021,13 +4161,13 @@
         <v>229</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4035,13 +4175,13 @@
         <v>229</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4049,13 +4189,13 @@
         <v>229</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4063,13 +4203,13 @@
         <v>229</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4077,13 +4217,13 @@
         <v>229</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4091,13 +4231,13 @@
         <v>229</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4105,13 +4245,13 @@
         <v>229</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4119,13 +4259,13 @@
         <v>229</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4133,13 +4273,13 @@
         <v>229</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4147,13 +4287,13 @@
         <v>229</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4161,13 +4301,13 @@
         <v>229</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4175,13 +4315,13 @@
         <v>229</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -4189,13 +4329,13 @@
         <v>229</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4203,13 +4343,13 @@
         <v>229</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4217,13 +4357,13 @@
         <v>229</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4231,13 +4371,13 @@
         <v>229</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4245,13 +4385,13 @@
         <v>229</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -4259,13 +4399,13 @@
         <v>229</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4273,13 +4413,13 @@
         <v>229</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4287,13 +4427,13 @@
         <v>229</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4301,13 +4441,13 @@
         <v>229</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -4315,13 +4455,13 @@
         <v>229</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -4329,13 +4469,13 @@
         <v>229</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -4343,13 +4483,13 @@
         <v>229</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -4357,13 +4497,13 @@
         <v>229</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -4371,13 +4511,13 @@
         <v>229</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -4385,13 +4525,13 @@
         <v>229</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -4399,13 +4539,13 @@
         <v>229</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -4413,13 +4553,13 @@
         <v>229</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4427,13 +4567,13 @@
         <v>229</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4441,10 +4581,10 @@
         <v>229</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>141</v>
@@ -4455,13 +4595,13 @@
         <v>229</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4469,13 +4609,13 @@
         <v>229</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -4483,13 +4623,13 @@
         <v>229</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4497,13 +4637,13 @@
         <v>229</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4511,13 +4651,13 @@
         <v>229</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4525,13 +4665,13 @@
         <v>229</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -4539,13 +4679,13 @@
         <v>229</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -4553,13 +4693,13 @@
         <v>229</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -4567,13 +4707,13 @@
         <v>229</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4581,13 +4721,13 @@
         <v>229</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4595,13 +4735,13 @@
         <v>229</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4609,13 +4749,13 @@
         <v>229</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4623,13 +4763,13 @@
         <v>229</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4637,13 +4777,13 @@
         <v>229</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -4651,13 +4791,13 @@
         <v>229</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4665,13 +4805,13 @@
         <v>229</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4679,13 +4819,13 @@
         <v>229</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>177</v>
+        <v>223</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>177</v>
+        <v>223</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -4693,13 +4833,13 @@
         <v>229</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4707,13 +4847,13 @@
         <v>229</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4721,13 +4861,13 @@
         <v>229</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4735,13 +4875,13 @@
         <v>229</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -4749,13 +4889,13 @@
         <v>229</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4763,13 +4903,13 @@
         <v>229</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4777,13 +4917,13 @@
         <v>229</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4791,13 +4931,13 @@
         <v>229</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -4805,13 +4945,13 @@
         <v>229</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4819,13 +4959,13 @@
         <v>229</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>66</v>
+        <v>227</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>66</v>
+        <v>227</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4833,13 +4973,13 @@
         <v>229</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4847,13 +4987,13 @@
         <v>229</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>66</v>
+        <v>228</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>66</v>
+        <v>228</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4861,10 +5001,10 @@
         <v>229</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>139</v>
@@ -4881,7 +5021,7 @@
         <v>66</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4895,7 +5035,7 @@
         <v>66</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4909,7 +5049,7 @@
         <v>66</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4923,7 +5063,7 @@
         <v>66</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4937,7 +5077,7 @@
         <v>66</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -4951,7 +5091,7 @@
         <v>66</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4965,7 +5105,7 @@
         <v>66</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -4979,7 +5119,7 @@
         <v>66</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -4993,7 +5133,7 @@
         <v>66</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -5007,7 +5147,7 @@
         <v>66</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -5021,7 +5161,7 @@
         <v>66</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -5035,7 +5175,7 @@
         <v>66</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -5049,7 +5189,7 @@
         <v>66</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -5063,7 +5203,7 @@
         <v>66</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -5077,7 +5217,7 @@
         <v>66</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -5091,7 +5231,7 @@
         <v>66</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -5105,7 +5245,7 @@
         <v>66</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -5119,7 +5259,7 @@
         <v>66</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -5133,7 +5273,7 @@
         <v>66</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -5147,7 +5287,7 @@
         <v>66</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5161,7 +5301,7 @@
         <v>66</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5175,7 +5315,7 @@
         <v>66</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -5189,7 +5329,7 @@
         <v>66</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -5203,7 +5343,7 @@
         <v>66</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -5217,7 +5357,7 @@
         <v>66</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -5231,91 +5371,91 @@
         <v>66</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B232" s="3">
-        <v>101</v>
-      </c>
-      <c r="C232" s="3">
-        <v>101</v>
-      </c>
-      <c r="G232" s="3" t="s">
-        <v>199</v>
+        <v>229</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B233" s="3">
-        <v>102</v>
-      </c>
-      <c r="C233" s="3">
-        <v>102</v>
-      </c>
-      <c r="G233" s="3" t="s">
-        <v>176</v>
+        <v>229</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B234" s="3">
-        <v>103</v>
-      </c>
-      <c r="C234" s="3">
-        <v>103</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>166</v>
+        <v>229</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B235" s="3">
-        <v>104</v>
-      </c>
-      <c r="C235" s="3">
-        <v>104</v>
-      </c>
-      <c r="G235" s="3" t="s">
-        <v>210</v>
+        <v>229</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B236" s="3">
-        <v>105</v>
-      </c>
-      <c r="C236" s="3">
-        <v>105</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
-      <c r="A237" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B237" s="3">
-        <v>106</v>
-      </c>
-      <c r="C237" s="3">
-        <v>106</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>178</v>
+        <v>229</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -5323,13 +5463,13 @@
         <v>230</v>
       </c>
       <c r="B238" s="3">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C238" s="3">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -5337,13 +5477,13 @@
         <v>230</v>
       </c>
       <c r="B239" s="3">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C239" s="3">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>220</v>
+        <v>176</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -5351,13 +5491,13 @@
         <v>230</v>
       </c>
       <c r="B240" s="3">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C240" s="3">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -5365,13 +5505,13 @@
         <v>230</v>
       </c>
       <c r="B241" s="3">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C241" s="3">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -5379,13 +5519,13 @@
         <v>230</v>
       </c>
       <c r="B242" s="3">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C242" s="3">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -5393,13 +5533,13 @@
         <v>230</v>
       </c>
       <c r="B243" s="3">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C243" s="3">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -5407,13 +5547,13 @@
         <v>230</v>
       </c>
       <c r="B244" s="3">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C244" s="3">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -5421,13 +5561,13 @@
         <v>230</v>
       </c>
       <c r="B245" s="3">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C245" s="3">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -5435,13 +5575,13 @@
         <v>230</v>
       </c>
       <c r="B246" s="3">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C246" s="3">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -5449,13 +5589,13 @@
         <v>230</v>
       </c>
       <c r="B247" s="3">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C247" s="3">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -5463,13 +5603,13 @@
         <v>230</v>
       </c>
       <c r="B248" s="3">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C248" s="3">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -5477,13 +5617,13 @@
         <v>230</v>
       </c>
       <c r="B249" s="3">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C249" s="3">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -5491,13 +5631,13 @@
         <v>230</v>
       </c>
       <c r="B250" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C250" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -5505,13 +5645,13 @@
         <v>230</v>
       </c>
       <c r="B251" s="3">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C251" s="3">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -5519,13 +5659,13 @@
         <v>230</v>
       </c>
       <c r="B252" s="3">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C252" s="3">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -5533,13 +5673,13 @@
         <v>230</v>
       </c>
       <c r="B253" s="3">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C253" s="3">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -5547,13 +5687,13 @@
         <v>230</v>
       </c>
       <c r="B254" s="3">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C254" s="3">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -5561,13 +5701,13 @@
         <v>230</v>
       </c>
       <c r="B255" s="3">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C255" s="3">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -5575,13 +5715,13 @@
         <v>230</v>
       </c>
       <c r="B256" s="3">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C256" s="3">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -5589,13 +5729,13 @@
         <v>230</v>
       </c>
       <c r="B257" s="3">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C257" s="3">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -5603,13 +5743,13 @@
         <v>230</v>
       </c>
       <c r="B258" s="3">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C258" s="3">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -5617,13 +5757,13 @@
         <v>230</v>
       </c>
       <c r="B259" s="3">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C259" s="3">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -5631,13 +5771,13 @@
         <v>230</v>
       </c>
       <c r="B260" s="3">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C260" s="3">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>176</v>
+        <v>222</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -5645,13 +5785,13 @@
         <v>230</v>
       </c>
       <c r="B261" s="3">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C261" s="3">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -5659,13 +5799,13 @@
         <v>230</v>
       </c>
       <c r="B262" s="3">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C262" s="3">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -5673,13 +5813,13 @@
         <v>230</v>
       </c>
       <c r="B263" s="3">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C263" s="3">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>166</v>
+        <v>224</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -5687,13 +5827,13 @@
         <v>230</v>
       </c>
       <c r="B264" s="3">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C264" s="3">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -5701,13 +5841,13 @@
         <v>230</v>
       </c>
       <c r="B265" s="3">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C265" s="3">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -5715,13 +5855,13 @@
         <v>230</v>
       </c>
       <c r="B266" s="3">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C266" s="3">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -5729,13 +5869,13 @@
         <v>230</v>
       </c>
       <c r="B267" s="3">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C267" s="3">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -5743,13 +5883,13 @@
         <v>230</v>
       </c>
       <c r="B268" s="3">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C268" s="3">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -5757,13 +5897,13 @@
         <v>230</v>
       </c>
       <c r="B269" s="3">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C269" s="3">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -5771,13 +5911,13 @@
         <v>230</v>
       </c>
       <c r="B270" s="3">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C270" s="3">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -5785,13 +5925,13 @@
         <v>230</v>
       </c>
       <c r="B271" s="3">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C271" s="3">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -5799,13 +5939,13 @@
         <v>230</v>
       </c>
       <c r="B272" s="3">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C272" s="3">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -5813,13 +5953,13 @@
         <v>230</v>
       </c>
       <c r="B273" s="3">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C273" s="3">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -5827,13 +5967,13 @@
         <v>230</v>
       </c>
       <c r="B274" s="3">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C274" s="3">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -5841,13 +5981,13 @@
         <v>230</v>
       </c>
       <c r="B275" s="3">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C275" s="3">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -5855,13 +5995,13 @@
         <v>230</v>
       </c>
       <c r="B276" s="3">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C276" s="3">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -5869,13 +6009,13 @@
         <v>230</v>
       </c>
       <c r="B277" s="3">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C277" s="3">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -5883,13 +6023,13 @@
         <v>230</v>
       </c>
       <c r="B278" s="3">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C278" s="3">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -5897,13 +6037,13 @@
         <v>230</v>
       </c>
       <c r="B279" s="3">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C279" s="3">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -5911,13 +6051,13 @@
         <v>230</v>
       </c>
       <c r="B280" s="3">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C280" s="3">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -5925,13 +6065,13 @@
         <v>230</v>
       </c>
       <c r="B281" s="3">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C281" s="3">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -5939,13 +6079,13 @@
         <v>230</v>
       </c>
       <c r="B282" s="3">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C282" s="3">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -5953,13 +6093,13 @@
         <v>230</v>
       </c>
       <c r="B283" s="3">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C283" s="3">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -5967,13 +6107,13 @@
         <v>230</v>
       </c>
       <c r="B284" s="3">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C284" s="3">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -5981,13 +6121,13 @@
         <v>230</v>
       </c>
       <c r="B285" s="3">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C285" s="3">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -5995,13 +6135,13 @@
         <v>230</v>
       </c>
       <c r="B286" s="3">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C286" s="3">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -6009,13 +6149,13 @@
         <v>230</v>
       </c>
       <c r="B287" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C287" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -6023,13 +6163,13 @@
         <v>230</v>
       </c>
       <c r="B288" s="3">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C288" s="3">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -6037,10 +6177,10 @@
         <v>230</v>
       </c>
       <c r="B289" s="3">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C289" s="3">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G289" s="3" t="s">
         <v>168</v>
@@ -6051,13 +6191,13 @@
         <v>230</v>
       </c>
       <c r="B290" s="3">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C290" s="3">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -6065,13 +6205,13 @@
         <v>230</v>
       </c>
       <c r="B291" s="3">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C291" s="3">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -6079,13 +6219,13 @@
         <v>230</v>
       </c>
       <c r="B292" s="3">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C292" s="3">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -6093,13 +6233,13 @@
         <v>230</v>
       </c>
       <c r="B293" s="3">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C293" s="3">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -6107,13 +6247,13 @@
         <v>230</v>
       </c>
       <c r="B294" s="3">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C294" s="3">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -6121,13 +6261,13 @@
         <v>230</v>
       </c>
       <c r="B295" s="3">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C295" s="3">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -6135,13 +6275,13 @@
         <v>230</v>
       </c>
       <c r="B296" s="3">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C296" s="3">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -6149,13 +6289,13 @@
         <v>230</v>
       </c>
       <c r="B297" s="3">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C297" s="3">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -6163,13 +6303,13 @@
         <v>230</v>
       </c>
       <c r="B298" s="3">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C298" s="3">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -6177,13 +6317,13 @@
         <v>230</v>
       </c>
       <c r="B299" s="3">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C299" s="3">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -6191,13 +6331,13 @@
         <v>230</v>
       </c>
       <c r="B300" s="3">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C300" s="3">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -6205,13 +6345,13 @@
         <v>230</v>
       </c>
       <c r="B301" s="3">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C301" s="3">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -6219,13 +6359,13 @@
         <v>230</v>
       </c>
       <c r="B302" s="3">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C302" s="3">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G302" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -6233,13 +6373,13 @@
         <v>230</v>
       </c>
       <c r="B303" s="3">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C303" s="3">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G303" s="3" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -6247,13 +6387,13 @@
         <v>230</v>
       </c>
       <c r="B304" s="3">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C304" s="3">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G304" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -6261,13 +6401,13 @@
         <v>230</v>
       </c>
       <c r="B305" s="3">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C305" s="3">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G305" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -6275,13 +6415,13 @@
         <v>230</v>
       </c>
       <c r="B306" s="3">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C306" s="3">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G306" s="3" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -6289,13 +6429,13 @@
         <v>230</v>
       </c>
       <c r="B307" s="3">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C307" s="3">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G307" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -6303,13 +6443,13 @@
         <v>230</v>
       </c>
       <c r="B308" s="3">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C308" s="3">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -6317,10 +6457,10 @@
         <v>230</v>
       </c>
       <c r="B309" s="3">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C309" s="3">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G309" s="3" t="s">
         <v>191</v>
@@ -6331,13 +6471,13 @@
         <v>230</v>
       </c>
       <c r="B310" s="3">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C310" s="3">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G310" s="3" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -6345,13 +6485,13 @@
         <v>230</v>
       </c>
       <c r="B311" s="3">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C311" s="3">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G311" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -6359,13 +6499,13 @@
         <v>230</v>
       </c>
       <c r="B312" s="3">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C312" s="3">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G312" s="3" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -6373,13 +6513,13 @@
         <v>230</v>
       </c>
       <c r="B313" s="3">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C313" s="3">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G313" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -6387,13 +6527,13 @@
         <v>230</v>
       </c>
       <c r="B314" s="3">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C314" s="3">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G314" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -6401,13 +6541,13 @@
         <v>230</v>
       </c>
       <c r="B315" s="3">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C315" s="3">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G315" s="3" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -6415,13 +6555,13 @@
         <v>230</v>
       </c>
       <c r="B316" s="3">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C316" s="3">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G316" s="3" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -6429,13 +6569,13 @@
         <v>230</v>
       </c>
       <c r="B317" s="3">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C317" s="3">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G317" s="3" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -6443,13 +6583,13 @@
         <v>230</v>
       </c>
       <c r="B318" s="3">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C318" s="3">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G318" s="3" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -6457,13 +6597,13 @@
         <v>230</v>
       </c>
       <c r="B319" s="3">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C319" s="3">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G319" s="3" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -6471,13 +6611,13 @@
         <v>230</v>
       </c>
       <c r="B320" s="3">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C320" s="3">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G320" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -6485,13 +6625,13 @@
         <v>230</v>
       </c>
       <c r="B321" s="3">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C321" s="3">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G321" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -6499,13 +6639,13 @@
         <v>230</v>
       </c>
       <c r="B322" s="3">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C322" s="3">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G322" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -6513,13 +6653,13 @@
         <v>230</v>
       </c>
       <c r="B323" s="3">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C323" s="3">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G323" s="3" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -6527,10 +6667,10 @@
         <v>230</v>
       </c>
       <c r="B324" s="3">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C324" s="3">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G324" s="3" t="s">
         <v>192</v>
@@ -6541,13 +6681,13 @@
         <v>230</v>
       </c>
       <c r="B325" s="3">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C325" s="3">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G325" s="3" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -6555,13 +6695,13 @@
         <v>230</v>
       </c>
       <c r="B326" s="3">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C326" s="3">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G326" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -6569,13 +6709,13 @@
         <v>230</v>
       </c>
       <c r="B327" s="3">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C327" s="3">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G327" s="3" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
     </row>
     <row r="328" spans="1:7">
@@ -6583,13 +6723,13 @@
         <v>230</v>
       </c>
       <c r="B328" s="3">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C328" s="3">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G328" s="3" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -6597,13 +6737,13 @@
         <v>230</v>
       </c>
       <c r="B329" s="3">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C329" s="3">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G329" s="3" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -6611,13 +6751,13 @@
         <v>230</v>
       </c>
       <c r="B330" s="3">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C330" s="3">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G330" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -6625,1818 +6765,1902 @@
         <v>230</v>
       </c>
       <c r="B331" s="3">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C331" s="3">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G331" s="3" t="s">
-        <v>169</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B332" s="3">
+        <v>195</v>
+      </c>
+      <c r="C332" s="3">
+        <v>195</v>
+      </c>
+      <c r="G332" s="3" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="333" spans="1:7">
       <c r="A333" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B333" s="3">
-        <v>101</v>
-      </c>
-      <c r="C333" s="3" t="str">
-        <f>_xlfn.CONCAT(B333, " (", F333, ")")</f>
-        <v>101 (Mvog-Ada)</v>
-      </c>
-      <c r="F333" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
+      </c>
+      <c r="C333" s="3">
+        <v>196</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B334" s="3">
-        <v>102</v>
-      </c>
-      <c r="C334" s="3" t="str">
-        <f t="shared" ref="C334:C397" si="0">_xlfn.CONCAT(B334, " (", F334, ")")</f>
-        <v>102 (Karen)</v>
-      </c>
-      <c r="F334" s="3" t="s">
-        <v>162</v>
+        <v>197</v>
+      </c>
+      <c r="C334" s="3">
+        <v>197</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="335" spans="1:7">
       <c r="A335" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B335" s="3">
+        <v>198</v>
+      </c>
+      <c r="C335" s="3">
+        <v>198</v>
+      </c>
+      <c r="G335" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B336" s="3">
+        <v>199</v>
+      </c>
+      <c r="C336" s="3">
+        <v>199</v>
+      </c>
+      <c r="G336" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B337" s="3">
+        <v>200</v>
+      </c>
+      <c r="C337" s="3">
+        <v>200</v>
+      </c>
+      <c r="G337" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B339" s="3">
+        <v>101</v>
+      </c>
+      <c r="C339" s="3" t="str">
+        <f>_xlfn.CONCAT(B339, " (", F339, ")")</f>
+        <v>101 (Mvog-Ada)</v>
+      </c>
+      <c r="F339" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G339" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B340" s="3">
+        <v>102</v>
+      </c>
+      <c r="C340" s="3" t="str">
+        <f t="shared" ref="C340:C403" si="0">_xlfn.CONCAT(B340, " (", F340, ")")</f>
+        <v>102 (Karen)</v>
+      </c>
+      <c r="F340" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G340" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B341" s="3">
         <v>103</v>
       </c>
-      <c r="C335" s="3" t="str">
+      <c r="C341" s="3" t="str">
         <f t="shared" si="0"/>
         <v>103 (Arada)</v>
       </c>
-      <c r="F335" s="3" t="s">
+      <c r="F341" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G335" s="3" t="s">
+      <c r="G341" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
-      <c r="A336" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B336" s="3">
+    <row r="342" spans="1:7">
+      <c r="A342" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B342" s="3">
         <v>104</v>
       </c>
-      <c r="C336" s="3" t="str">
+      <c r="C342" s="3" t="str">
         <f t="shared" si="0"/>
         <v>104 (Soweto)</v>
       </c>
-      <c r="F336" s="3" t="s">
+      <c r="F342" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G336" s="3" t="s">
+      <c r="G342" s="3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
-      <c r="A337" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B337" s="3">
+    <row r="343" spans="1:7">
+      <c r="A343" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B343" s="3">
         <v>105</v>
       </c>
-      <c r="C337" s="3" t="str">
+      <c r="C343" s="3" t="str">
         <f t="shared" si="0"/>
         <v>105 (Talangaï)</v>
       </c>
-      <c r="F337" s="3" t="s">
+      <c r="F343" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G337" s="3" t="s">
+      <c r="G343" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
-      <c r="A338" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B338" s="3">
+    <row r="344" spans="1:7">
+      <c r="A344" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B344" s="3">
         <v>106</v>
       </c>
-      <c r="C338" s="3" t="str">
+      <c r="C344" s="3" t="str">
         <f t="shared" si="0"/>
         <v>106 (Osu)</v>
       </c>
-      <c r="F338" s="3" t="s">
+      <c r="F344" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G338" s="3" t="s">
+      <c r="G344" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
-      <c r="A339" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B339" s="3">
+    <row r="345" spans="1:7">
+      <c r="A345" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B345" s="3">
         <v>107</v>
       </c>
-      <c r="C339" s="3" t="str">
+      <c r="C345" s="3" t="str">
         <f t="shared" si="0"/>
         <v>107 (Yeka)</v>
       </c>
-      <c r="F339" s="3" t="s">
+      <c r="F345" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G339" s="3" t="s">
+      <c r="G345" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
-      <c r="A340" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B340" s="3">
+    <row r="346" spans="1:7">
+      <c r="A346" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B346" s="3">
         <v>108</v>
       </c>
-      <c r="C340" s="3" t="str">
+      <c r="C346" s="3" t="str">
         <f t="shared" si="0"/>
         <v>108 (Soweto)</v>
       </c>
-      <c r="F340" s="3" t="s">
+      <c r="F346" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G340" s="3" t="s">
+      <c r="G346" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
-      <c r="A341" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B341" s="3">
+    <row r="347" spans="1:7">
+      <c r="A347" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B347" s="3">
         <v>109</v>
       </c>
-      <c r="C341" s="3" t="str">
+      <c r="C347" s="3" t="str">
         <f t="shared" si="0"/>
         <v>109 (Osu)</v>
       </c>
-      <c r="F341" s="3" t="s">
+      <c r="F347" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G341" s="3" t="s">
+      <c r="G347" s="3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
-      <c r="A342" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B342" s="3">
+    <row r="348" spans="1:7">
+      <c r="A348" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B348" s="3">
         <v>110</v>
       </c>
-      <c r="C342" s="3" t="str">
+      <c r="C348" s="3" t="str">
         <f t="shared" si="0"/>
         <v>110 (Bole)</v>
       </c>
-      <c r="F342" s="3" t="s">
+      <c r="F348" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G342" s="3" t="s">
+      <c r="G348" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
-      <c r="A343" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B343" s="3">
+    <row r="349" spans="1:7">
+      <c r="A349" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B349" s="3">
         <v>111</v>
       </c>
-      <c r="C343" s="3" t="str">
+      <c r="C349" s="3" t="str">
         <f t="shared" si="0"/>
         <v>111 (Karen)</v>
       </c>
-      <c r="F343" s="3" t="s">
+      <c r="F349" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G343" s="3" t="s">
+      <c r="G349" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
-      <c r="A344" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B344" s="3">
+    <row r="350" spans="1:7">
+      <c r="A350" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B350" s="3">
         <v>112</v>
       </c>
-      <c r="C344" s="3" t="str">
+      <c r="C350" s="3" t="str">
         <f t="shared" si="0"/>
         <v>112 (Poto-Poto)</v>
       </c>
-      <c r="F344" s="3" t="s">
+      <c r="F350" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G344" s="3" t="s">
+      <c r="G350" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
-      <c r="A345" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B345" s="3">
+    <row r="351" spans="1:7">
+      <c r="A351" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B351" s="3">
         <v>113</v>
       </c>
-      <c r="C345" s="3" t="str">
+      <c r="C351" s="3" t="str">
         <f t="shared" si="0"/>
         <v>113 (Randburg)</v>
       </c>
-      <c r="F345" s="3" t="s">
+      <c r="F351" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G345" s="3" t="s">
+      <c r="G351" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
-      <c r="A346" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B346" s="3">
+    <row r="352" spans="1:7">
+      <c r="A352" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B352" s="3">
         <v>114</v>
       </c>
-      <c r="C346" s="3" t="str">
+      <c r="C352" s="3" t="str">
         <f t="shared" si="0"/>
         <v>114 (Labadi)</v>
       </c>
-      <c r="F346" s="3" t="s">
+      <c r="F352" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G346" s="3" t="s">
+      <c r="G352" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
-      <c r="A347" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B347" s="3">
+    <row r="353" spans="1:7">
+      <c r="A353" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B353" s="3">
         <v>115</v>
       </c>
-      <c r="C347" s="3" t="str">
+      <c r="C353" s="3" t="str">
         <f t="shared" si="0"/>
         <v>115 (Essos)</v>
       </c>
-      <c r="F347" s="3" t="s">
+      <c r="F353" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G347" s="3" t="s">
+      <c r="G353" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
-      <c r="A348" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B348" s="3">
+    <row r="354" spans="1:7">
+      <c r="A354" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B354" s="3">
         <v>116</v>
       </c>
-      <c r="C348" s="3" t="str">
+      <c r="C354" s="3" t="str">
         <f t="shared" si="0"/>
         <v>116 (Arada)</v>
       </c>
-      <c r="F348" s="3" t="s">
+      <c r="F354" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G348" s="3" t="s">
+      <c r="G354" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
-      <c r="A349" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B349" s="3">
+    <row r="355" spans="1:7">
+      <c r="A355" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B355" s="3">
         <v>117</v>
       </c>
-      <c r="C349" s="3" t="str">
+      <c r="C355" s="3" t="str">
         <f t="shared" si="0"/>
         <v>117 (Poto-Poto)</v>
       </c>
-      <c r="F349" s="3" t="s">
+      <c r="F355" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G349" s="3" t="s">
+      <c r="G355" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
-      <c r="A350" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B350" s="3">
+    <row r="356" spans="1:7">
+      <c r="A356" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B356" s="3">
         <v>118</v>
       </c>
-      <c r="C350" s="3" t="str">
+      <c r="C356" s="3" t="str">
         <f t="shared" si="0"/>
         <v>118 (Ikeja)</v>
       </c>
-      <c r="F350" s="3" t="s">
+      <c r="F356" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G350" s="3" t="s">
+      <c r="G356" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
-      <c r="A351" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B351" s="3">
+    <row r="357" spans="1:7">
+      <c r="A357" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B357" s="3">
         <v>119</v>
       </c>
-      <c r="C351" s="3" t="str">
+      <c r="C357" s="3" t="str">
         <f t="shared" si="0"/>
         <v>119 (Gombe)</v>
       </c>
-      <c r="F351" s="3" t="s">
+      <c r="F357" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G351" s="3" t="s">
+      <c r="G357" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
-      <c r="A352" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B352" s="3">
+    <row r="358" spans="1:7">
+      <c r="A358" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B358" s="3">
         <v>120</v>
       </c>
-      <c r="C352" s="3" t="str">
+      <c r="C358" s="3" t="str">
         <f t="shared" si="0"/>
         <v>120 (Nakawa)</v>
       </c>
-      <c r="F352" s="3" t="s">
+      <c r="F358" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G352" s="3" t="s">
+      <c r="G358" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
-      <c r="A353" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B353" s="3">
+    <row r="359" spans="1:7">
+      <c r="A359" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B359" s="3">
         <v>121</v>
       </c>
-      <c r="C353" s="3" t="str">
+      <c r="C359" s="3" t="str">
         <f t="shared" si="0"/>
         <v>121 (Bacongo)</v>
       </c>
-      <c r="F353" s="3" t="s">
+      <c r="F359" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G353" s="3" t="s">
+      <c r="G359" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
-      <c r="A354" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B354" s="3">
+    <row r="360" spans="1:7">
+      <c r="A360" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B360" s="3">
         <v>122</v>
       </c>
-      <c r="C354" s="3" t="str">
+      <c r="C360" s="3" t="str">
         <f t="shared" si="0"/>
         <v>122 (Poto-Poto)</v>
       </c>
-      <c r="F354" s="3" t="s">
+      <c r="F360" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G354" s="3" t="s">
+      <c r="G360" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
-      <c r="A355" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B355" s="3">
+    <row r="361" spans="1:7">
+      <c r="A361" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B361" s="3">
         <v>123</v>
       </c>
-      <c r="C355" s="3" t="str">
+      <c r="C361" s="3" t="str">
         <f t="shared" si="0"/>
         <v>123 (Surulere)</v>
       </c>
-      <c r="F355" s="3" t="s">
+      <c r="F361" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G355" s="3" t="s">
+      <c r="G361" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
-      <c r="A356" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B356" s="3">
+    <row r="362" spans="1:7">
+      <c r="A362" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B362" s="3">
         <v>124</v>
       </c>
-      <c r="C356" s="3" t="str">
+      <c r="C362" s="3" t="str">
         <f t="shared" si="0"/>
         <v>124 (Nakawa)</v>
       </c>
-      <c r="F356" s="3" t="s">
+      <c r="F362" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G356" s="3" t="s">
+      <c r="G362" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
-      <c r="A357" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B357" s="3">
+    <row r="363" spans="1:7">
+      <c r="A363" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B363" s="3">
         <v>125</v>
       </c>
-      <c r="C357" s="3" t="str">
+      <c r="C363" s="3" t="str">
         <f t="shared" si="0"/>
         <v>125 (Ikeja)</v>
       </c>
-      <c r="F357" s="3" t="s">
+      <c r="F363" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G357" s="3" t="s">
+      <c r="G363" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
-      <c r="A358" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B358" s="3">
+    <row r="364" spans="1:7">
+      <c r="A364" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B364" s="3">
         <v>126</v>
       </c>
-      <c r="C358" s="3" t="str">
+      <c r="C364" s="3" t="str">
         <f t="shared" si="0"/>
         <v>126 (Talangaï)</v>
       </c>
-      <c r="F358" s="3" t="s">
+      <c r="F364" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G358" s="3" t="s">
+      <c r="G364" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
-      <c r="A359" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B359" s="3">
+    <row r="365" spans="1:7">
+      <c r="A365" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B365" s="3">
         <v>127</v>
       </c>
-      <c r="C359" s="3" t="str">
+      <c r="C365" s="3" t="str">
         <f t="shared" si="0"/>
         <v>127 (Chilenje)</v>
       </c>
-      <c r="F359" s="3" t="s">
+      <c r="F365" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G359" s="3" t="s">
+      <c r="G365" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
-      <c r="A360" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B360" s="3">
+    <row r="366" spans="1:7">
+      <c r="A366" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B366" s="3">
         <v>128</v>
       </c>
-      <c r="C360" s="3" t="str">
+      <c r="C366" s="3" t="str">
         <f t="shared" si="0"/>
         <v>128 (Poto-Poto)</v>
       </c>
-      <c r="F360" s="3" t="s">
+      <c r="F366" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G360" s="3" t="s">
+      <c r="G366" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
-      <c r="A361" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B361" s="3">
+    <row r="367" spans="1:7">
+      <c r="A367" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B367" s="3">
         <v>129</v>
       </c>
-      <c r="C361" s="3" t="str">
+      <c r="C367" s="3" t="str">
         <f t="shared" si="0"/>
         <v>129 (Borrowdale)</v>
       </c>
-      <c r="F361" s="3" t="s">
+      <c r="F367" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G361" s="3" t="s">
+      <c r="G367" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
-      <c r="A362" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B362" s="3">
+    <row r="368" spans="1:7">
+      <c r="A368" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B368" s="3">
         <v>130</v>
       </c>
-      <c r="C362" s="3" t="str">
+      <c r="C368" s="3" t="str">
         <f t="shared" si="0"/>
         <v>130 (Yaba)</v>
       </c>
-      <c r="F362" s="3" t="s">
+      <c r="F368" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G362" s="3" t="s">
+      <c r="G368" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
-      <c r="A363" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B363" s="3">
+    <row r="369" spans="1:7">
+      <c r="A369" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B369" s="3">
         <v>131</v>
       </c>
-      <c r="C363" s="3" t="str">
+      <c r="C369" s="3" t="str">
         <f t="shared" si="0"/>
         <v>131 (Mvog-Ada)</v>
       </c>
-      <c r="F363" s="3" t="s">
+      <c r="F369" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G363" s="3" t="s">
+      <c r="G369" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
-      <c r="A364" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B364" s="3">
+    <row r="370" spans="1:7">
+      <c r="A370" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B370" s="3">
         <v>132</v>
       </c>
-      <c r="C364" s="3" t="str">
+      <c r="C370" s="3" t="str">
         <f t="shared" si="0"/>
         <v>132 (Mvog-Ada)</v>
       </c>
-      <c r="F364" s="3" t="s">
+      <c r="F370" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G364" s="3" t="s">
+      <c r="G370" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
-      <c r="A365" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B365" s="3">
+    <row r="371" spans="1:7">
+      <c r="A371" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B371" s="3">
         <v>133</v>
       </c>
-      <c r="C365" s="3" t="str">
+      <c r="C371" s="3" t="str">
         <f t="shared" si="0"/>
         <v>133 (Labadi)</v>
       </c>
-      <c r="F365" s="3" t="s">
+      <c r="F371" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G365" s="3" t="s">
+      <c r="G371" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
-      <c r="A366" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B366" s="3">
+    <row r="372" spans="1:7">
+      <c r="A372" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B372" s="3">
         <v>134</v>
       </c>
-      <c r="C366" s="3" t="str">
+      <c r="C372" s="3" t="str">
         <f t="shared" si="0"/>
         <v>134 (Poto-Poto)</v>
       </c>
-      <c r="F366" s="3" t="s">
+      <c r="F372" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G366" s="3" t="s">
+      <c r="G372" s="3" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
-      <c r="A367" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B367" s="3">
+    <row r="373" spans="1:7">
+      <c r="A373" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B373" s="3">
         <v>135</v>
       </c>
-      <c r="C367" s="3" t="str">
+      <c r="C373" s="3" t="str">
         <f t="shared" si="0"/>
         <v>135 (Madina)</v>
       </c>
-      <c r="F367" s="3" t="s">
+      <c r="F373" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G367" s="3" t="s">
+      <c r="G373" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
-      <c r="A368" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B368" s="3">
+    <row r="374" spans="1:7">
+      <c r="A374" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B374" s="3">
         <v>136</v>
       </c>
-      <c r="C368" s="3" t="str">
+      <c r="C374" s="3" t="str">
         <f t="shared" si="0"/>
         <v>136 (Labadi)</v>
       </c>
-      <c r="F368" s="3" t="s">
+      <c r="F374" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G368" s="3" t="s">
+      <c r="G374" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
-      <c r="A369" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B369" s="3">
+    <row r="375" spans="1:7">
+      <c r="A375" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B375" s="3">
         <v>137</v>
       </c>
-      <c r="C369" s="3" t="str">
+      <c r="C375" s="3" t="str">
         <f t="shared" si="0"/>
         <v>137 (Randburg)</v>
       </c>
-      <c r="F369" s="3" t="s">
+      <c r="F375" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G369" s="3" t="s">
+      <c r="G375" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
-      <c r="A370" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B370" s="3">
+    <row r="376" spans="1:7">
+      <c r="A376" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B376" s="3">
         <v>138</v>
       </c>
-      <c r="C370" s="3" t="str">
+      <c r="C376" s="3" t="str">
         <f t="shared" si="0"/>
         <v>138 (Bole)</v>
       </c>
-      <c r="F370" s="3" t="s">
+      <c r="F376" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G370" s="3" t="s">
+      <c r="G376" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
-      <c r="A371" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B371" s="3">
+    <row r="377" spans="1:7">
+      <c r="A377" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B377" s="3">
         <v>139</v>
       </c>
-      <c r="C371" s="3" t="str">
+      <c r="C377" s="3" t="str">
         <f t="shared" si="0"/>
         <v>139 (Ikeja)</v>
       </c>
-      <c r="F371" s="3" t="s">
+      <c r="F377" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G371" s="3" t="s">
+      <c r="G377" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
-      <c r="A372" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B372" s="3">
+    <row r="378" spans="1:7">
+      <c r="A378" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B378" s="3">
         <v>140</v>
       </c>
-      <c r="C372" s="3" t="str">
+      <c r="C378" s="3" t="str">
         <f t="shared" si="0"/>
         <v>140 (Talangaï)</v>
       </c>
-      <c r="F372" s="3" t="s">
+      <c r="F378" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G372" s="3" t="s">
+      <c r="G378" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
-      <c r="A373" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B373" s="3">
+    <row r="379" spans="1:7">
+      <c r="A379" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B379" s="3">
         <v>141</v>
       </c>
-      <c r="C373" s="3" t="str">
+      <c r="C379" s="3" t="str">
         <f t="shared" si="0"/>
         <v>141 (Gombe)</v>
       </c>
-      <c r="F373" s="3" t="s">
+      <c r="F379" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G373" s="3" t="s">
+      <c r="G379" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
-      <c r="A374" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B374" s="3">
+    <row r="380" spans="1:7">
+      <c r="A380" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B380" s="3">
         <v>142</v>
       </c>
-      <c r="C374" s="3" t="str">
+      <c r="C380" s="3" t="str">
         <f t="shared" si="0"/>
         <v>142 (Medina)</v>
       </c>
-      <c r="F374" s="3" t="s">
+      <c r="F380" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G374" s="3" t="s">
+      <c r="G380" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
-      <c r="A375" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B375" s="3">
+    <row r="381" spans="1:7">
+      <c r="A381" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B381" s="3">
         <v>143</v>
       </c>
-      <c r="C375" s="3" t="str">
+      <c r="C381" s="3" t="str">
         <f t="shared" si="0"/>
         <v>143 (Medina)</v>
       </c>
-      <c r="F375" s="3" t="s">
+      <c r="F381" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G375" s="3" t="s">
+      <c r="G381" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
-      <c r="A376" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B376" s="3">
+    <row r="382" spans="1:7">
+      <c r="A382" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B382" s="3">
         <v>144</v>
       </c>
-      <c r="C376" s="3" t="str">
+      <c r="C382" s="3" t="str">
         <f t="shared" si="0"/>
         <v>144 (Randburg)</v>
       </c>
-      <c r="F376" s="3" t="s">
+      <c r="F382" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G376" s="3" t="s">
+      <c r="G382" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
-      <c r="A377" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B377" s="3">
+    <row r="383" spans="1:7">
+      <c r="A383" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B383" s="3">
         <v>145</v>
       </c>
-      <c r="C377" s="3" t="str">
+      <c r="C383" s="3" t="str">
         <f t="shared" si="0"/>
         <v>145 (Sandton)</v>
       </c>
-      <c r="F377" s="3" t="s">
+      <c r="F383" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G377" s="3" t="s">
+      <c r="G383" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
-      <c r="A378" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B378" s="3">
+    <row r="384" spans="1:7">
+      <c r="A384" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B384" s="3">
         <v>146</v>
       </c>
-      <c r="C378" s="3" t="str">
+      <c r="C384" s="3" t="str">
         <f t="shared" si="0"/>
         <v>146 (Yeka)</v>
       </c>
-      <c r="F378" s="3" t="s">
+      <c r="F384" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G378" s="3" t="s">
+      <c r="G384" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
-      <c r="A379" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B379" s="3">
+    <row r="385" spans="1:7">
+      <c r="A385" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B385" s="3">
         <v>147</v>
       </c>
-      <c r="C379" s="3" t="str">
+      <c r="C385" s="3" t="str">
         <f t="shared" si="0"/>
         <v>147 (Makindye)</v>
       </c>
-      <c r="F379" s="3" t="s">
+      <c r="F385" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G379" s="3" t="s">
+      <c r="G385" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
-      <c r="A380" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B380" s="3">
+    <row r="386" spans="1:7">
+      <c r="A386" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B386" s="3">
         <v>148</v>
       </c>
-      <c r="C380" s="3" t="str">
+      <c r="C386" s="3" t="str">
         <f t="shared" si="0"/>
         <v>148 (Gombe)</v>
       </c>
-      <c r="F380" s="3" t="s">
+      <c r="F386" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G380" s="3" t="s">
+      <c r="G386" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
-      <c r="A381" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B381" s="3">
+    <row r="387" spans="1:7">
+      <c r="A387" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B387" s="3">
         <v>149</v>
       </c>
-      <c r="C381" s="3" t="str">
+      <c r="C387" s="3" t="str">
         <f t="shared" si="0"/>
         <v>149 (Yeka)</v>
       </c>
-      <c r="F381" s="3" t="s">
+      <c r="F387" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G381" s="3" t="s">
+      <c r="G387" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
-      <c r="A382" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B382" s="3">
+    <row r="388" spans="1:7">
+      <c r="A388" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B388" s="3">
         <v>150</v>
       </c>
-      <c r="C382" s="3" t="str">
+      <c r="C388" s="3" t="str">
         <f t="shared" si="0"/>
         <v>150 (Ikeja)</v>
       </c>
-      <c r="F382" s="3" t="s">
+      <c r="F388" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G382" s="3" t="s">
+      <c r="G388" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
-      <c r="A383" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B383" s="3">
+    <row r="389" spans="1:7">
+      <c r="A389" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B389" s="3">
         <v>151</v>
       </c>
-      <c r="C383" s="3" t="str">
+      <c r="C389" s="3" t="str">
         <f t="shared" si="0"/>
         <v>151 (Poto-Poto)</v>
       </c>
-      <c r="F383" s="3" t="s">
+      <c r="F389" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G383" s="3" t="s">
+      <c r="G389" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
-      <c r="A384" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B384" s="3">
+    <row r="390" spans="1:7">
+      <c r="A390" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B390" s="3">
         <v>152</v>
       </c>
-      <c r="C384" s="3" t="str">
+      <c r="C390" s="3" t="str">
         <f t="shared" si="0"/>
         <v>152 (Bacongo)</v>
       </c>
-      <c r="F384" s="3" t="s">
+      <c r="F390" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G384" s="3" t="s">
+      <c r="G390" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
-      <c r="A385" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B385" s="3">
+    <row r="391" spans="1:7">
+      <c r="A391" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B391" s="3">
         <v>153</v>
       </c>
-      <c r="C385" s="3" t="str">
+      <c r="C391" s="3" t="str">
         <f t="shared" si="0"/>
         <v>153 (Gombe)</v>
       </c>
-      <c r="F385" s="3" t="s">
+      <c r="F391" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G385" s="3" t="s">
+      <c r="G391" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
-      <c r="A386" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B386" s="3">
+    <row r="392" spans="1:7">
+      <c r="A392" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B392" s="3">
         <v>154</v>
       </c>
-      <c r="C386" s="3" t="str">
+      <c r="C392" s="3" t="str">
         <f t="shared" si="0"/>
         <v>154 (Bole)</v>
       </c>
-      <c r="F386" s="3" t="s">
+      <c r="F392" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G386" s="3" t="s">
+      <c r="G392" s="3" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
-      <c r="A387" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B387" s="3">
+    <row r="393" spans="1:7">
+      <c r="A393" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B393" s="3">
         <v>155</v>
       </c>
-      <c r="C387" s="3" t="str">
+      <c r="C393" s="3" t="str">
         <f t="shared" si="0"/>
         <v>155 (Talangaï)</v>
       </c>
-      <c r="F387" s="3" t="s">
+      <c r="F393" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G387" s="3" t="s">
+      <c r="G393" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
-      <c r="A388" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B388" s="3">
+    <row r="394" spans="1:7">
+      <c r="A394" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B394" s="3">
         <v>156</v>
       </c>
-      <c r="C388" s="3" t="str">
+      <c r="C394" s="3" t="str">
         <f t="shared" si="0"/>
         <v>156 (Matero)</v>
       </c>
-      <c r="F388" s="3" t="s">
+      <c r="F394" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G388" s="3" t="s">
+      <c r="G394" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
-      <c r="A389" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B389" s="3">
+    <row r="395" spans="1:7">
+      <c r="A395" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B395" s="3">
         <v>157</v>
       </c>
-      <c r="C389" s="3" t="str">
+      <c r="C395" s="3" t="str">
         <f t="shared" si="0"/>
         <v>157 (Yaba)</v>
       </c>
-      <c r="F389" s="3" t="s">
+      <c r="F395" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G389" s="3" t="s">
+      <c r="G395" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
-      <c r="A390" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B390" s="3">
+    <row r="396" spans="1:7">
+      <c r="A396" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B396" s="3">
         <v>158</v>
       </c>
-      <c r="C390" s="3" t="str">
+      <c r="C396" s="3" t="str">
         <f t="shared" si="0"/>
         <v>158 (Matero)</v>
       </c>
-      <c r="F390" s="3" t="s">
+      <c r="F396" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G390" s="3" t="s">
+      <c r="G396" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
-      <c r="A391" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B391" s="3">
+    <row r="397" spans="1:7">
+      <c r="A397" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B397" s="3">
         <v>159</v>
       </c>
-      <c r="C391" s="3" t="str">
+      <c r="C397" s="3" t="str">
         <f t="shared" si="0"/>
         <v>159 (Plateau)</v>
       </c>
-      <c r="F391" s="3" t="s">
+      <c r="F397" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G391" s="3" t="s">
+      <c r="G397" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
-      <c r="A392" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B392" s="3">
+    <row r="398" spans="1:7">
+      <c r="A398" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B398" s="3">
         <v>160</v>
       </c>
-      <c r="C392" s="3" t="str">
+      <c r="C398" s="3" t="str">
         <f t="shared" si="0"/>
         <v>160 (Karen)</v>
       </c>
-      <c r="F392" s="3" t="s">
+      <c r="F398" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G392" s="3" t="s">
+      <c r="G398" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
-      <c r="A393" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B393" s="3">
+    <row r="399" spans="1:7">
+      <c r="A399" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B399" s="3">
         <v>161</v>
       </c>
-      <c r="C393" s="3" t="str">
+      <c r="C399" s="3" t="str">
         <f t="shared" si="0"/>
         <v>161 (Pikine)</v>
       </c>
-      <c r="F393" s="3" t="s">
+      <c r="F399" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G393" s="3" t="s">
+      <c r="G399" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
-      <c r="A394" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B394" s="3">
+    <row r="400" spans="1:7">
+      <c r="A400" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B400" s="3">
         <v>162</v>
       </c>
-      <c r="C394" s="3" t="str">
+      <c r="C400" s="3" t="str">
         <f t="shared" si="0"/>
         <v>162 (Matero)</v>
       </c>
-      <c r="F394" s="3" t="s">
+      <c r="F400" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G394" s="3" t="s">
+      <c r="G400" s="3" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
-      <c r="A395" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B395" s="3">
+    <row r="401" spans="1:7">
+      <c r="A401" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B401" s="3">
         <v>163</v>
       </c>
-      <c r="C395" s="3" t="str">
+      <c r="C401" s="3" t="str">
         <f t="shared" si="0"/>
         <v>163 (Madina)</v>
       </c>
-      <c r="F395" s="3" t="s">
+      <c r="F401" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G395" s="3" t="s">
+      <c r="G401" s="3" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
-      <c r="A396" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B396" s="3">
+    <row r="402" spans="1:7">
+      <c r="A402" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B402" s="3">
         <v>164</v>
       </c>
-      <c r="C396" s="3" t="str">
+      <c r="C402" s="3" t="str">
         <f t="shared" si="0"/>
         <v>164 (Surulere)</v>
       </c>
-      <c r="F396" s="3" t="s">
+      <c r="F402" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G396" s="3" t="s">
+      <c r="G402" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
-      <c r="A397" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B397" s="3">
+    <row r="403" spans="1:7">
+      <c r="A403" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B403" s="3">
         <v>165</v>
       </c>
-      <c r="C397" s="3" t="str">
+      <c r="C403" s="3" t="str">
         <f t="shared" si="0"/>
         <v>165 (Osu)</v>
       </c>
-      <c r="F397" s="3" t="s">
+      <c r="F403" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G397" s="3" t="s">
+      <c r="G403" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
-      <c r="A398" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B398" s="3">
+    <row r="404" spans="1:7">
+      <c r="A404" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B404" s="3">
         <v>166</v>
       </c>
-      <c r="C398" s="3" t="str">
-        <f t="shared" ref="C398:C432" si="1">_xlfn.CONCAT(B398, " (", F398, ")")</f>
+      <c r="C404" s="3" t="str">
+        <f t="shared" ref="C404:C438" si="1">_xlfn.CONCAT(B404, " (", F404, ")")</f>
         <v>166 (Pikine)</v>
       </c>
-      <c r="F398" s="3" t="s">
+      <c r="F404" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G398" s="3" t="s">
+      <c r="G404" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
-      <c r="A399" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B399" s="3">
+    <row r="405" spans="1:7">
+      <c r="A405" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B405" s="3">
         <v>167</v>
       </c>
-      <c r="C399" s="3" t="str">
+      <c r="C405" s="3" t="str">
         <f t="shared" si="1"/>
         <v>167 (Kibera)</v>
       </c>
-      <c r="F399" s="3" t="s">
+      <c r="F405" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G399" s="3" t="s">
+      <c r="G405" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
-      <c r="A400" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B400" s="3">
+    <row r="406" spans="1:7">
+      <c r="A406" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B406" s="3">
         <v>168</v>
       </c>
-      <c r="C400" s="3" t="str">
+      <c r="C406" s="3" t="str">
         <f t="shared" si="1"/>
         <v>168 (Nakawa)</v>
       </c>
-      <c r="F400" s="3" t="s">
+      <c r="F406" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G400" s="3" t="s">
+      <c r="G406" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
-      <c r="A401" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B401" s="3">
+    <row r="407" spans="1:7">
+      <c r="A407" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B407" s="3">
         <v>169</v>
       </c>
-      <c r="C401" s="3" t="str">
+      <c r="C407" s="3" t="str">
         <f t="shared" si="1"/>
         <v>169 (Gombe)</v>
       </c>
-      <c r="F401" s="3" t="s">
+      <c r="F407" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G401" s="3" t="s">
+      <c r="G407" s="3" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
-      <c r="A402" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B402" s="3">
+    <row r="408" spans="1:7">
+      <c r="A408" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B408" s="3">
         <v>170</v>
       </c>
-      <c r="C402" s="3" t="str">
+      <c r="C408" s="3" t="str">
         <f t="shared" si="1"/>
         <v>170 (Makindye)</v>
       </c>
-      <c r="F402" s="3" t="s">
+      <c r="F408" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G402" s="3" t="s">
+      <c r="G408" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
-      <c r="A403" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B403" s="3">
+    <row r="409" spans="1:7">
+      <c r="A409" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B409" s="3">
         <v>171</v>
       </c>
-      <c r="C403" s="3" t="str">
+      <c r="C409" s="3" t="str">
         <f t="shared" si="1"/>
         <v>171 (Mvog-Ada)</v>
       </c>
-      <c r="F403" s="3" t="s">
+      <c r="F409" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G403" s="3" t="s">
+      <c r="G409" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
-      <c r="A404" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B404" s="3">
+    <row r="410" spans="1:7">
+      <c r="A410" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B410" s="3">
         <v>172</v>
       </c>
-      <c r="C404" s="3" t="str">
+      <c r="C410" s="3" t="str">
         <f t="shared" si="1"/>
         <v>172 (Kabulonga)</v>
       </c>
-      <c r="F404" s="3" t="s">
+      <c r="F410" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G404" s="3" t="s">
+      <c r="G410" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
-      <c r="A405" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B405" s="3">
+    <row r="411" spans="1:7">
+      <c r="A411" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B411" s="3">
         <v>173</v>
       </c>
-      <c r="C405" s="3" t="str">
+      <c r="C411" s="3" t="str">
         <f t="shared" si="1"/>
         <v>173 (Matero)</v>
       </c>
-      <c r="F405" s="3" t="s">
+      <c r="F411" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G405" s="3" t="s">
+      <c r="G411" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
-      <c r="A406" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B406" s="3">
+    <row r="412" spans="1:7">
+      <c r="A412" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B412" s="3">
         <v>174</v>
       </c>
-      <c r="C406" s="3" t="str">
+      <c r="C412" s="3" t="str">
         <f t="shared" si="1"/>
         <v>174 (Essos)</v>
       </c>
-      <c r="F406" s="3" t="s">
+      <c r="F412" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G406" s="3" t="s">
+      <c r="G412" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
-      <c r="A407" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B407" s="3">
+    <row r="413" spans="1:7">
+      <c r="A413" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B413" s="3">
         <v>175</v>
       </c>
-      <c r="C407" s="3" t="str">
+      <c r="C413" s="3" t="str">
         <f t="shared" si="1"/>
         <v>175 (Talangaï)</v>
       </c>
-      <c r="F407" s="3" t="s">
+      <c r="F413" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G407" s="3" t="s">
+      <c r="G413" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
-      <c r="A408" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B408" s="3">
+    <row r="414" spans="1:7">
+      <c r="A414" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B414" s="3">
         <v>176</v>
       </c>
-      <c r="C408" s="3" t="str">
+      <c r="C414" s="3" t="str">
         <f t="shared" si="1"/>
         <v>176 (Mvog-Ada)</v>
       </c>
-      <c r="F408" s="3" t="s">
+      <c r="F414" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G408" s="3" t="s">
+      <c r="G414" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
-      <c r="A409" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B409" s="3">
+    <row r="415" spans="1:7">
+      <c r="A415" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B415" s="3">
         <v>177</v>
       </c>
-      <c r="C409" s="3" t="str">
+      <c r="C415" s="3" t="str">
         <f t="shared" si="1"/>
         <v>177 (Essos)</v>
       </c>
-      <c r="F409" s="3" t="s">
+      <c r="F415" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G409" s="3" t="s">
+      <c r="G415" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
-      <c r="A410" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B410" s="3">
+    <row r="416" spans="1:7">
+      <c r="A416" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B416" s="3">
         <v>178</v>
       </c>
-      <c r="C410" s="3" t="str">
+      <c r="C416" s="3" t="str">
         <f t="shared" si="1"/>
         <v>178 (Medina)</v>
       </c>
-      <c r="F410" s="3" t="s">
+      <c r="F416" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G410" s="3" t="s">
+      <c r="G416" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
-      <c r="A411" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B411" s="3">
+    <row r="417" spans="1:7">
+      <c r="A417" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B417" s="3">
         <v>179</v>
       </c>
-      <c r="C411" s="3" t="str">
+      <c r="C417" s="3" t="str">
         <f t="shared" si="1"/>
         <v>179 (Ikeja)</v>
       </c>
-      <c r="F411" s="3" t="s">
+      <c r="F417" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G411" s="3" t="s">
+      <c r="G417" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
-      <c r="A412" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B412" s="3">
+    <row r="418" spans="1:7">
+      <c r="A418" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B418" s="3">
         <v>180</v>
       </c>
-      <c r="C412" s="3" t="str">
+      <c r="C418" s="3" t="str">
         <f t="shared" si="1"/>
         <v>180 (Karen)</v>
       </c>
-      <c r="F412" s="3" t="s">
+      <c r="F418" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G412" s="3" t="s">
+      <c r="G418" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
-      <c r="A413" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B413" s="3">
+    <row r="419" spans="1:7">
+      <c r="A419" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B419" s="3">
         <v>181</v>
       </c>
-      <c r="C413" s="3" t="str">
+      <c r="C419" s="3" t="str">
         <f t="shared" si="1"/>
         <v>181 (Yaba)</v>
       </c>
-      <c r="F413" s="3" t="s">
+      <c r="F419" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G413" s="3" t="s">
+      <c r="G419" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
-      <c r="A414" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B414" s="3">
+    <row r="420" spans="1:7">
+      <c r="A420" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B420" s="3">
         <v>182</v>
       </c>
-      <c r="C414" s="3" t="str">
+      <c r="C420" s="3" t="str">
         <f t="shared" si="1"/>
         <v>182 (Randburg)</v>
       </c>
-      <c r="F414" s="3" t="s">
+      <c r="F420" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G414" s="3" t="s">
+      <c r="G420" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
-      <c r="A415" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B415" s="3">
+    <row r="421" spans="1:7">
+      <c r="A421" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B421" s="3">
         <v>183</v>
       </c>
-      <c r="C415" s="3" t="str">
+      <c r="C421" s="3" t="str">
         <f t="shared" si="1"/>
         <v>183 (Bole)</v>
       </c>
-      <c r="F415" s="3" t="s">
+      <c r="F421" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G415" s="3" t="s">
+      <c r="G421" s="3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
-      <c r="A416" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B416" s="3">
+    <row r="422" spans="1:7">
+      <c r="A422" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B422" s="3">
         <v>184</v>
       </c>
-      <c r="C416" s="3" t="str">
+      <c r="C422" s="3" t="str">
         <f t="shared" si="1"/>
         <v>184 (Yaba)</v>
       </c>
-      <c r="F416" s="3" t="s">
+      <c r="F422" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G416" s="3" t="s">
+      <c r="G422" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
-      <c r="A417" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B417" s="3">
+    <row r="423" spans="1:7">
+      <c r="A423" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B423" s="3">
         <v>185</v>
       </c>
-      <c r="C417" s="3" t="str">
+      <c r="C423" s="3" t="str">
         <f t="shared" si="1"/>
         <v>185 (Pikine)</v>
       </c>
-      <c r="F417" s="3" t="s">
+      <c r="F423" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G417" s="3" t="s">
+      <c r="G423" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
-      <c r="A418" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B418" s="3">
+    <row r="424" spans="1:7">
+      <c r="A424" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B424" s="3">
         <v>186</v>
       </c>
-      <c r="C418" s="3" t="str">
+      <c r="C424" s="3" t="str">
         <f t="shared" si="1"/>
         <v>186 (Talangaï)</v>
       </c>
-      <c r="F418" s="3" t="s">
+      <c r="F424" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G418" s="3" t="s">
+      <c r="G424" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
-      <c r="A419" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B419" s="3">
+    <row r="425" spans="1:7">
+      <c r="A425" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B425" s="3">
         <v>187</v>
       </c>
-      <c r="C419" s="3" t="str">
+      <c r="C425" s="3" t="str">
         <f t="shared" si="1"/>
         <v>187 (Karen)</v>
       </c>
-      <c r="F419" s="3" t="s">
+      <c r="F425" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G419" s="3" t="s">
+      <c r="G425" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
-      <c r="A420" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B420" s="3">
+    <row r="426" spans="1:7">
+      <c r="A426" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B426" s="3">
         <v>188</v>
       </c>
-      <c r="C420" s="3" t="str">
+      <c r="C426" s="3" t="str">
         <f t="shared" si="1"/>
         <v>188 (Madina)</v>
       </c>
-      <c r="F420" s="3" t="s">
+      <c r="F426" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G420" s="3" t="s">
+      <c r="G426" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
-      <c r="A421" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B421" s="3">
+    <row r="427" spans="1:7">
+      <c r="A427" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B427" s="3">
         <v>189</v>
       </c>
-      <c r="C421" s="3" t="str">
+      <c r="C427" s="3" t="str">
         <f t="shared" si="1"/>
         <v>189 (Kawempe)</v>
       </c>
-      <c r="F421" s="3" t="s">
+      <c r="F427" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G421" s="3" t="s">
+      <c r="G427" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
-      <c r="A422" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B422" s="3">
+    <row r="428" spans="1:7">
+      <c r="A428" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B428" s="3">
         <v>190</v>
       </c>
-      <c r="C422" s="3" t="str">
+      <c r="C428" s="3" t="str">
         <f t="shared" si="1"/>
         <v>190 (Sandton)</v>
       </c>
-      <c r="F422" s="3" t="s">
+      <c r="F428" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G422" s="3" t="s">
+      <c r="G428" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
-      <c r="A423" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B423" s="3">
+    <row r="429" spans="1:7">
+      <c r="A429" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B429" s="3">
         <v>191</v>
       </c>
-      <c r="C423" s="3" t="str">
+      <c r="C429" s="3" t="str">
         <f t="shared" si="1"/>
         <v>191 (Matete)</v>
       </c>
-      <c r="F423" s="3" t="s">
+      <c r="F429" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G423" s="3" t="s">
+      <c r="G429" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
-      <c r="A424" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B424" s="3">
+    <row r="430" spans="1:7">
+      <c r="A430" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B430" s="3">
         <v>192</v>
       </c>
-      <c r="C424" s="3" t="str">
+      <c r="C430" s="3" t="str">
         <f t="shared" si="1"/>
         <v>192 (Poto-Poto)</v>
       </c>
-      <c r="F424" s="3" t="s">
+      <c r="F430" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G424" s="3" t="s">
+      <c r="G430" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
-      <c r="A425" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B425" s="3">
+    <row r="431" spans="1:7">
+      <c r="A431" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B431" s="3">
         <v>193</v>
       </c>
-      <c r="C425" s="3" t="str">
+      <c r="C431" s="3" t="str">
         <f t="shared" si="1"/>
         <v>193 (Kabulonga)</v>
       </c>
-      <c r="F425" s="3" t="s">
+      <c r="F431" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G425" s="3" t="s">
+      <c r="G431" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
-      <c r="A426" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B426" s="3">
+    <row r="432" spans="1:7">
+      <c r="A432" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B432" s="3">
         <v>194</v>
       </c>
-      <c r="C426" s="3" t="str">
+      <c r="C432" s="3" t="str">
         <f t="shared" si="1"/>
         <v>194 (Surulere)</v>
       </c>
-      <c r="F426" s="3" t="s">
+      <c r="F432" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G426" s="3" t="s">
+      <c r="G432" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
-      <c r="A427" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B427" s="3">
+    <row r="433" spans="1:7">
+      <c r="A433" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B433" s="3">
         <v>195</v>
       </c>
-      <c r="C427" s="3" t="str">
+      <c r="C433" s="3" t="str">
         <f t="shared" si="1"/>
         <v>195 (Matero)</v>
       </c>
-      <c r="F427" s="3" t="s">
+      <c r="F433" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G427" s="3" t="s">
+      <c r="G433" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
-      <c r="A428" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B428" s="3">
+    <row r="434" spans="1:7">
+      <c r="A434" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B434" s="3">
         <v>196</v>
       </c>
-      <c r="C428" s="3" t="str">
+      <c r="C434" s="3" t="str">
         <f t="shared" si="1"/>
         <v>196 (Highfield)</v>
       </c>
-      <c r="F428" s="3" t="s">
+      <c r="F434" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G428" s="3" t="s">
+      <c r="G434" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
-      <c r="A429" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B429" s="3">
+    <row r="435" spans="1:7">
+      <c r="A435" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B435" s="3">
         <v>197</v>
       </c>
-      <c r="C429" s="3" t="str">
+      <c r="C435" s="3" t="str">
         <f t="shared" si="1"/>
         <v>197 (Bole)</v>
       </c>
-      <c r="F429" s="3" t="s">
+      <c r="F435" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G429" s="3" t="s">
+      <c r="G435" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
-      <c r="A430" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B430" s="3">
+    <row r="436" spans="1:7">
+      <c r="A436" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B436" s="3">
         <v>198</v>
       </c>
-      <c r="C430" s="3" t="str">
+      <c r="C436" s="3" t="str">
         <f t="shared" si="1"/>
         <v>198 (Pikine)</v>
       </c>
-      <c r="F430" s="3" t="s">
+      <c r="F436" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G430" s="3" t="s">
+      <c r="G436" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
-      <c r="A431" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B431" s="3">
+    <row r="437" spans="1:7">
+      <c r="A437" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B437" s="3">
         <v>199</v>
       </c>
-      <c r="C431" s="3" t="str">
+      <c r="C437" s="3" t="str">
         <f t="shared" si="1"/>
         <v>199 (Ikeja)</v>
       </c>
-      <c r="F431" s="3" t="s">
+      <c r="F437" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G431" s="3" t="s">
+      <c r="G437" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
-      <c r="A432" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B432" s="3">
+    <row r="438" spans="1:7">
+      <c r="A438" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B438" s="3">
         <v>200</v>
       </c>
-      <c r="C432" s="3" t="str">
+      <c r="C438" s="3" t="str">
         <f t="shared" si="1"/>
         <v>200 (Bacongo)</v>
       </c>
-      <c r="F432" s="3" t="s">
+      <c r="F438" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G432" s="3" t="s">
+      <c r="G438" s="3" t="s">
         <v>169</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:B52">
-    <sortCondition ref="B14:B52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:B58">
+    <sortCondition ref="B14:B58"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8450,7 +8674,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="73.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="39" style="3" customWidth="1"/>
+    <col min="2" max="2" width="40.875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" style="3" customWidth="1"/>
     <col min="4" max="16384" width="11" style="3"/>
   </cols>
@@ -8474,7 +8698,7 @@
         <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>73</v>

--- a/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_1_river_assess.xlsx
+++ b/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_1_river_assess.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\ONCHO\ento\river prospection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FFD7E3-0EA6-462A-852A-BF2C2C26A01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A473C95-271D-4414-93A1-D51D55BF3956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="316">
   <si>
     <t>type</t>
   </si>
@@ -977,6 +977,12 @@
   </si>
   <si>
     <t>More than 201</t>
+  </si>
+  <si>
+    <t>${s_site_suitability} = 'Yes'</t>
+  </si>
+  <si>
+    <t>${s_larvae_evidence} = 'Yes'</t>
   </si>
 </sst>
 </file>
@@ -1988,7 +1994,9 @@
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="23"/>
-      <c r="H20" s="22"/>
+      <c r="H20" s="22" t="s">
+        <v>314</v>
+      </c>
       <c r="I20" s="22"/>
       <c r="J20" s="22" t="s">
         <v>11</v>
@@ -2011,7 +2019,9 @@
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
       <c r="G21" s="23"/>
-      <c r="H21" s="22"/>
+      <c r="H21" s="22" t="s">
+        <v>315</v>
+      </c>
       <c r="I21" s="22"/>
       <c r="J21" s="22" t="s">
         <v>11</v>

--- a/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_1_river_assess.xlsx
+++ b/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_1_river_assess.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\ONCHO\ento\river prospection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A473C95-271D-4414-93A1-D51D55BF3956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D9DA7F-BB08-456A-91ED-CF37DAA988E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="318">
   <si>
     <t>type</t>
   </si>
@@ -983,6 +983,12 @@
   </si>
   <si>
     <t>${s_larvae_evidence} = 'Yes'</t>
+  </si>
+  <si>
+    <t>s_river_basin</t>
+  </si>
+  <si>
+    <t>River Basin</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26" style="3" customWidth="1"/>
@@ -1811,15 +1817,15 @@
       <c r="L12" s="21"/>
       <c r="M12" s="21"/>
     </row>
-    <row r="13" spans="1:13" s="4" customFormat="1" ht="31.5">
+    <row r="13" spans="1:13" s="4" customFormat="1">
       <c r="A13" s="21" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>101</v>
+        <v>317</v>
       </c>
       <c r="D13" s="23"/>
       <c r="E13" s="21"/>
@@ -1834,70 +1840,66 @@
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" s="4" customFormat="1">
+    <row r="14" spans="1:13" s="4" customFormat="1" ht="31.5">
       <c r="A14" s="21" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
       <c r="J14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="21"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="21"/>
       <c r="M14" s="21"/>
     </row>
     <row r="15" spans="1:13" s="4" customFormat="1">
       <c r="A15" s="21" t="s">
-        <v>289</v>
+        <v>22</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>283</v>
+        <v>23</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>287</v>
+        <v>102</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
       <c r="J15" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="22"/>
+      <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="21"/>
     </row>
     <row r="16" spans="1:13" s="4" customFormat="1">
       <c r="A16" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="21"/>
-      <c r="F16" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>292</v>
-      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="23"/>
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
       <c r="J16" s="22" t="s">
@@ -1909,21 +1911,21 @@
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1">
       <c r="A17" s="21" t="s">
-        <v>9</v>
+        <v>290</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="21"/>
       <c r="F17" s="21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H17" s="22"/>
       <c r="I17" s="22"/>
@@ -1936,18 +1938,22 @@
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1">
       <c r="A18" s="21" t="s">
-        <v>297</v>
+        <v>9</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="23"/>
+      <c r="F18" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>294</v>
+      </c>
       <c r="H18" s="22"/>
       <c r="I18" s="22"/>
       <c r="J18" s="22" t="s">
@@ -1957,15 +1963,15 @@
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
     </row>
-    <row r="19" spans="1:13" s="4" customFormat="1" ht="31.5">
+    <row r="19" spans="1:13" s="4" customFormat="1">
       <c r="A19" s="21" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="21"/>
@@ -1985,18 +1991,16 @@
         <v>305</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="23"/>
-      <c r="H20" s="22" t="s">
-        <v>314</v>
-      </c>
+      <c r="H20" s="22"/>
       <c r="I20" s="22"/>
       <c r="J20" s="22" t="s">
         <v>11</v>
@@ -2006,21 +2010,21 @@
       <c r="M20" s="21"/>
     </row>
     <row r="21" spans="1:13" s="4" customFormat="1" ht="31.5">
-      <c r="A21" s="32" t="s">
-        <v>306</v>
+      <c r="A21" s="21" t="s">
+        <v>305</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
       <c r="G21" s="23"/>
       <c r="H21" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I21" s="22"/>
       <c r="J21" s="22" t="s">
@@ -2030,42 +2034,44 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="21" t="s">
+    <row r="22" spans="1:13" s="4" customFormat="1" ht="31.5">
+      <c r="A22" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="D22" s="23"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="26" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="27"/>
+        <v>103</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>269</v>
+      </c>
       <c r="E23" s="26"/>
       <c r="F23" s="26"/>
       <c r="G23" s="27"/>
@@ -2080,13 +2086,13 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="26" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="26"/>
@@ -2103,13 +2109,13 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="26" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="26"/>
@@ -2117,20 +2123,22 @@
       <c r="G25" s="27"/>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
-      <c r="J25" s="21"/>
+      <c r="J25" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="K25" s="26"/>
       <c r="L25" s="26"/>
       <c r="M25" s="26"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="26" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="26"/>
@@ -2145,13 +2153,13 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="26" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="26"/>
@@ -2166,21 +2174,19 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="26" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="26"/>
       <c r="F28" s="26"/>
       <c r="G28" s="27"/>
-      <c r="H28" s="26" t="s">
-        <v>34</v>
-      </c>
+      <c r="H28" s="26"/>
       <c r="I28" s="26"/>
       <c r="J28" s="21"/>
       <c r="K28" s="26"/>
@@ -2189,67 +2195,67 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="26" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>270</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D29" s="27"/>
       <c r="E29" s="26"/>
       <c r="F29" s="26"/>
       <c r="G29" s="27"/>
-      <c r="H29" s="26"/>
+      <c r="H29" s="26" t="s">
+        <v>34</v>
+      </c>
       <c r="I29" s="26"/>
-      <c r="J29" s="21" t="s">
-        <v>11</v>
-      </c>
+      <c r="J29" s="21"/>
       <c r="K29" s="26"/>
       <c r="L29" s="26"/>
       <c r="M29" s="26"/>
     </row>
-    <row r="30" spans="1:13" s="4" customFormat="1">
-      <c r="A30" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
+    <row r="30" spans="1:13">
+      <c r="A30" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" s="4" customFormat="1">
       <c r="A31" s="21" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
       <c r="G31" s="24"/>
-      <c r="H31" s="26" t="s">
-        <v>40</v>
-      </c>
+      <c r="H31" s="21"/>
       <c r="I31" s="21"/>
       <c r="J31" s="22"/>
       <c r="K31" s="21"/>
@@ -2258,17 +2264,21 @@
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1">
       <c r="A32" s="21" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>112</v>
+      </c>
       <c r="D32" s="23"/>
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="24"/>
-      <c r="H32" s="21"/>
+      <c r="H32" s="26" t="s">
+        <v>40</v>
+      </c>
       <c r="I32" s="21"/>
       <c r="J32" s="22"/>
       <c r="K32" s="21"/>
@@ -2277,10 +2287,10 @@
     </row>
     <row r="33" spans="1:13" s="4" customFormat="1">
       <c r="A33" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
@@ -2295,9 +2305,23 @@
       <c r="M33" s="21"/>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1">
-      <c r="B34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="G34" s="3"/>
+      <c r="A34" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1">
       <c r="B35" s="7"/>
@@ -2305,9 +2329,14 @@
       <c r="G35" s="3"/>
     </row>
     <row r="36" spans="1:13" s="4" customFormat="1">
-      <c r="B36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="7"/>
+      <c r="D36" s="7"/>
       <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:13" s="4" customFormat="1">
+      <c r="B37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="G37" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
